--- a/邊坡資料.xlsx
+++ b/邊坡資料.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jenhanchang/SA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{53D441C7-973A-4248-AAE0-5A2319FA6BE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C3DF65B9-91EB-9143-B51C-6CC1B8787EF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="820" yWindow="880" windowWidth="35180" windowHeight="22500" xr2:uid="{21FCCB7F-B956-8047-BAE8-4AD674EF40B8}"/>
+    <workbookView xWindow="820" yWindow="880" windowWidth="35180" windowHeight="22500" xr2:uid="{A041BC7A-12CC-3E4C-A1AF-B96C7640476C}"/>
   </bookViews>
   <sheets>
     <sheet name="邊坡資料" sheetId="1" r:id="rId1"/>
@@ -370,10 +370,10 @@
     <t>106/04</t>
   </si>
   <si>
-    <t>岩屑崩滑高敏感區(105K+950-107K+100)。順向坡(105K+980-106K+050)。山崩與地滑地質敏感區(106K+100-106K+800)。 --------------------------------------------------------------- 已納入105年3月自然災害(107.01-107.09)邊坡於106年4月修復完成。 災害與時間：105.3豪雨災害 災點：(舊樁號107K+010~177K+600) 災害編號：105-04-B23 已修復竣事 --------------------------------------------------------------- 災害與時間：110.10.13豪雨災害 災點：4K+250上邊坡 災害編號：110-04-B37 施作項目：刷坡1130m2、掛網及錨筋灌漿1130m2 開始施作時間：110.10 完成施作時間：111.03 --------------------------------------------------------------- 災害與時間：112.02.08豪雨災害 災點：4K+500上邊坡 災害編號：112-04-B09 施作項目：刷坡1000m2、型框植生1000m2 開始施作時間：112.04 完成施作時間：112.07 延至4K+600匡列災點</t>
-  </si>
-  <si>
-    <t>2026/9/24 上午 10:53:01</t>
+    <t>岩屑崩滑高敏感區(105K+950-107K+100)。順向坡(105K+980-106K+050)。山崩與地滑地質敏感區(106K+100-106K+800)。 --------------------------------------------------------------- 已納入105年3月自然災害(107.01-107.09)邊坡於106年4月修復完成。 災害與時間：105.3豪雨災害 災點：(舊樁號107K+010~177K+600) 災害編號：105-04-B23 已修復竣事 --------------------------------------------------------------- 災害與時間：110.10.13豪雨災害 災點：4K+250上邊坡 災害編號：110-04-B37 施作項目：刷坡1130m2、掛網及錨筋灌漿1130m2 開始施作時間：110.10 完成施作時間：111.03 --------------------------------------------------------------- 災害與時間：112.02.08豪雨災害 災點：4K+500上邊坡 災害編號：112-04-B09 施作項目：刷坡1000m2、型框植生1000m2 開始施作時間：112.04 完成施作時間：112.07 延至4K+600匡列災點 ---------------</t>
+  </si>
+  <si>
+    <t>2026/10/17 下午 02:56:18</t>
   </si>
   <si>
     <t>0209DX-003600-D0-00-00000</t>
@@ -436,10 +436,10 @@
     <t>10503自然災害 1140330豪雨災害</t>
   </si>
   <si>
-    <t>岩屑崩滑高敏感區(107K+600-108K+200)。山崩與地滑地質敏感區(107K+600-108K+000)。 已納入105年3月自然災害(107.81K-107.84K)於106年4月邊坡修復完成。 --------------------------------------------------------------- ---------------------------------------------------- 災害與時間：114.3.30 災點：台9丁5.2k 災害編號：114-04-B29 施作項目：型框植生 開始施作時間：114.1.25 完成施作時間：114.5.14</t>
-  </si>
-  <si>
-    <t>2026/5/20 下午 03:04:56</t>
+    <t>岩屑崩滑高敏感區(107K+600-108K+200)。山崩與地滑地質敏感區(107K+600-108K+000)。 已納入105年3月自然災害(107.81K-107.84K)於106年4月邊坡修復完成。 --------------------------------------------------------------- 災害與時間：114.3.30 災點：台9丁5.2k 災害編號：114-04-B29 施作項目：型框植生 開始施作時間：114.1.25 完成施作時間：114.5.14</t>
+  </si>
+  <si>
+    <t>2026/10/14 下午 09:23:15</t>
   </si>
   <si>
     <t>0209DX-005600-A0-00-00000</t>
@@ -463,7 +463,7 @@
     <t>山崩與地滑地質敏感區(108K+400~108K+600，108K+900~109K+300)。)。岩屑崩滑高敏感區(108K+480~109K+920)。落石高敏感區(108K+980~109K+280)。 邊坡無明顯不穩定徵兆。 --------------------------------------------------------------- 災害與時間：108.4.26豪雨災害 災點：6K+065、6K+160上邊坡 災害編號：108-04-B19 施作項目：縱洩溝100M2、邊坡掛網及錨筋灌漿420M2 --------------------------------------------------------------- 災害與時間：114年11月鳳凰颱風豪雨災害 災點：台9丁線5k+600上邊坡 災害編號：115-04-B01 施作項目：型框植生187m2 施作時間: 115.1.10 完成時間:115.3.5</t>
   </si>
   <si>
-    <t>2026/5/19 下午 03:57:47</t>
+    <t>2026/10/17 下午 02:54:08</t>
   </si>
   <si>
     <t>0209DX-006680-D0-00-00000</t>
@@ -568,16 +568,16 @@
     <t>東南</t>
   </si>
   <si>
-    <t>10912豪雨災害 11208豪雨災害 114年11月鳳凰颱風豪雨災害</t>
+    <t>10912豪雨災害 11208豪雨災害 114年11月鳳凰颱風豪雨災害 115年3月5日豪雨災害</t>
   </si>
   <si>
     <t>109/12</t>
   </si>
   <si>
-    <t>--------------------------------------------------------- 災害與時間：109.12.23豪雨災害 災點：8K+870、8K+970下邊坡 災害編號：110-04-B11 施作項目：微型樁加擋土牆 完成施作時間：110.11 --------------------------------------------------------- 災害與時間：112.8.17豪雨災害 災點：8K+900下邊坡 災害編號：112-04-B31 施作項目：張力開列固結灌漿 開始施作時間：112.10 完成施作時間：113.10 --------------------------------------------------------- 災害與時間：114年11月鳳凰颱風豪雨災害 災點：8K+900下邊坡 災害編號：115-04-A08 施作項目：格梁護坡、下邊坡全套管基樁、預力地錨 預定開始施作時間：115.11 完成施作時間：</t>
-  </si>
-  <si>
-    <t>2026/5/20 下午 03:22:15</t>
+    <t>--------------------------------------------------------- 災害與時間：109.12.23豪雨災害 災點：8K+870、8K+970下邊坡 災害編號：110-04-B11 施作項目：微型樁加擋土牆 完成施作時間：110.11 --------------------------------------------------------- 災害與時間：112.8.17豪雨災害 災點：8K+900下邊坡 災害編號：112-04-B31 施作項目：張力開列固結灌漿 開始施作時間：112.10 完成施作時間：113.10 --------------------------------------------------------- 災害與時間：114年11月鳳凰颱風豪雨災害 災點：8K+900下邊坡 災害編號：115-04-A08 施作項目：格梁護坡、下邊坡全套管基樁、預力地錨 預計開始施作時間：116.1 預計完成施作時間：117.4 --------------------------------------------------------- 災害與時間：115年3月5日豪雨災害 災點：8K+900下邊坡 災害編號：115-04-B2 施作項目：臨時性預力地錨(30噸)25支@2m 開始施作時間：115.8 預計完成施作時間：115.12</t>
+  </si>
+  <si>
+    <t>2026/10/17 下午 02:09:10</t>
   </si>
   <si>
     <t>0209DX-009200-A0-00-00000</t>
@@ -592,7 +592,7 @@
     <t>東北</t>
   </si>
   <si>
-    <t>106年5月28日坍方 107年07月16日豪雨災害 107年11月09日豪雨災害 107年12月29日豪雨災害 108.04.16豪雨災害 109年7月1日自然災害 1130724凱米颱風 114年11月鳳凰颱風豪雨災害</t>
+    <t>106年5月28日坍方 107年07月16日豪雨災害 107年11月09日豪雨災害 107年12月29日豪雨災害 108.04.16豪雨災害 109年7月1日自然災害 1130724凱米颱風 114年11月鳳凰颱風豪雨災害 115年3月5日豪雨災害</t>
   </si>
   <si>
     <t>106/03(概估)</t>
@@ -601,10 +601,10 @@
     <t>九宮里</t>
   </si>
   <si>
-    <t>山崩與地滑地質敏感區(111K+400~114K+000)。岩屑崩滑高敏感區(112K+050-112K+470)。落石高敏感區(112K+350-112K+950)。 ---------------------------------------------------- 災害與時間： 災點：113K+300上邊坡 開始施作時間：106.02 完成施作時間：106.03 ---------------------------------------------------- 災害與時間：106年5月28日坍方 災點：(112K+600)上邊坡 災害編號：106-04-A06 、106-04-A07 ---------------------------------------------------- 災害與時間：107年07月16日豪雨災害 災點：10K+100上邊坡、9K+800上邊坡 災害編號：107-04-B27 施作項目：掛網及錨筋灌漿、防落石柵 ---------------------------------------------------- 災害與時間：107年11月09日豪雨災害 災點：9K+800邊溝 災害編號：107-04-B43 施作項目：邊溝修復 ---------------------------------------------------- 災害與時間：107年12月29日豪雨災害 災點：9K+300上邊坡 災害編號：108-04-B05 施作項目：掛網及錨筋灌漿 完成施作時間：108.04 ---------------------------------------------------- 災害與時間：108.04.16豪雨災害 災點：9k+300~9k+311下邊坡 災害編號：108-04-B19 施作項目：縱洩溝 ---------------------------------------------------- 災害與時間：109年7月1日自然災害 災點：10K+020上邊坡 災害編號：109-04-B13 施作項目：邊坡掛網 開始施作時間：109.09 完成施作時間：109.11 ---------------------------------------------------- 災害與時間：113.07.24凱米颱風 災點：9K+500上邊坡 災害編號：113-04-A22 施作項目：刷坡7175m2、縱洩溝3775M2、掛網3200m2 開始施作時間：113.09 完成施作時間：114.8.24 ---------------------------------------------------- 災害與時間：114年11月鳳凰颱風豪雨災害 災點：9K+500上邊坡 災害編號：115-04-A08 施作項目：型框植生 預定開始施作時間：115.11 預定完成施作時間：</t>
-  </si>
-  <si>
-    <t>2026/5/26 上午 10:32:30</t>
+    <t>山崩與地滑地質敏感區(111K+400~114K+000)。岩屑崩滑高敏感區(112K+050-112K+470)。落石高敏感區(112K+350-112K+950)。 ---------------------------------------------------- 災害與時間： 災點：113K+300上邊坡 開始施作時間：106.02 完成施作時間：106.03 ---------------------------------------------------- 災害與時間：106年5月28日坍方 災點：(112K+600)上邊坡 災害編號：106-04-A06 、106-04-A07 ---------------------------------------------------- 災害與時間：107年07月16日豪雨災害 災點：10K+100上邊坡、9K+800上邊坡 災害編號：107-04-B27 施作項目：掛網及錨筋灌漿、防落石柵 ---------------------------------------------------- 災害與時間：107年11月09日豪雨災害 災點：9K+800邊溝 災害編號：107-04-B43 施作項目：邊溝修復 ---------------------------------------------------- 災害與時間：107年12月29日豪雨災害 災點：9K+300上邊坡 災害編號：108-04-B05 施作項目：掛網及錨筋灌漿 完成施作時間：108.04 ---------------------------------------------------- 災害與時間：108.04.16豪雨災害 災點：9k+300~9k+311下邊坡 災害編號：108-04-B19 施作項目：縱洩溝 ---------------------------------------------------- 災害與時間：109年7月1日自然災害 災點：10K+020上邊坡 災害編號：109-04-B13 施作項目：邊坡掛網 開始施作時間：109.09 完成施作時間：109.11 ---------------------------------------------------- 災害與時間：113.07.24凱米颱風 災點：9K+500上邊坡 災害編號：113-04-A22 施作項目：刷坡7175m2、縱洩溝3775M2、掛網3200m2 開始施作時間：113.09 完成施作時間：114.8.24 ---------------------------------------------------- 災害與時間：114年11月鳳凰颱風豪雨災害 災點：9K+500上邊坡 災害編號：115-04-A08 施作項目：型框植生 預定開始施作時間：116.1 預定完成施作時間：116.12 ---------------------------------------------------- 災害與時間：115年3月5日豪雨災害 災點：9K+400下邊坡 災害編號：115-04-B02 施作項目：3m*3m橫向箱涵、鋪設瀝青634.5T、鋼管護欄10M、下邊坡跌水工縱洩溝300m2 開始施作時間：115.8 預定完成施作時間：115.12</t>
+  </si>
+  <si>
+    <t>2026/10/17 下午 02:07:25</t>
   </si>
   <si>
     <t>0209DX-010005-D0-00-00000</t>
@@ -664,10 +664,10 @@
     <t>山崩與地滑地質敏感區,順向坡</t>
   </si>
   <si>
-    <t>山崩與地滑地質敏感區(111K+400~114K+000)。岩屑崩滑高敏感區：112K+970-114K+020。 --------------------------------------------------------------- 災害與時間：105年9月梅姬風災 災點：(舊樁號114.03~114.05) ----------------------------------- 災害與時間：105年11月23日豪雨災害 災點：(舊樁號113K+350~400) 災害編號：105-04-B30 ------------------------------------------------------------- 災害與時間：106年3月份豪雨災害 災點：(舊樁號112K+300) 災害編號：105-04-B30 ------------------------------------------------------------ 災害與時間：106年5月28日坍方災害 災點：(舊樁號112K+600) 施作項目：噴凝土及邊坡防落石網 完成施作時間：107.12 ----------------------------------------------------------- 災害與時間：106年10月11日豪雨災害 災點：(舊樁號113K+130、113K+400、114K+070、141K+150) 災害編號：106-04-B25 --------------------------------------------------------------- 災害與時間：109.12.23豪雨災害 災點：11K+300上邊坡 災害編號：110-04-B11 施作項目：型框植生 完成施作時間：110.06 --------------------------------------------------------------- 災害與時間：111.10.10豪雨災害 災點：11K+200上邊坡 災害編號：111-04-B40 施作項目：型框植生612m2、縱洩(橫截)溝88m2 開始施作時間：111.11 完成施作時間：112.07 --------------------------------------------------------------- 災害與時間：113.04.03地震災害 災點：11K+150上邊坡 災害編號：113-04-B14 施作項目：刷坡1600m2、掛網及錨筋灌漿1600m2 開始施作時間：113.04 完成施作時間：113.10 --------------------------------------------------------------- 災害與時間：113.04.03地震災害 災點：11K+300上邊坡 災害編號：113-04-B14 施作項目：刷坡1500m2、型框植生1500m2 開始施作時間：113.04 完成施作時間：113.08 --------------------------------------------------------------- 災害與時間：114年11月鳳凰颱風豪雨災害 災點：10K+400上邊坡 災害編號：115-04-B01 施作項目：型框植生1211m2、懸眺步道修復135m 預定開始施作時間：115.06 預計完成施作時間：115.09</t>
-  </si>
-  <si>
-    <t>2026/5/20 下午 03:24:36</t>
+    <t>山崩與地滑地質敏感區(111K+400~114K+000)。岩屑崩滑高敏感區：112K+970-114K+020。 --------------------------------------------------------------- 災害與時間：105年9月梅姬風災 災點：(舊樁號114.03~114.05) ----------------------------------- 災害與時間：105年11月23日豪雨災害 災點：(舊樁號113K+350~400) 災害編號：105-04-B30 ------------------------------------------------------------- 災害與時間：106年3月份豪雨災害 災點：(舊樁號112K+300) 災害編號：105-04-B30 ------------------------------------------------------------ 災害與時間：106年5月28日坍方災害 災點：(舊樁號112K+600) 施作項目：噴凝土及邊坡防落石網 完成施作時間：107.12 ----------------------------------------------------------- 災害與時間：106年10月11日豪雨災害 災點：(舊樁號113K+130、113K+400、114K+070、141K+150) 災害編號：106-04-B25 --------------------------------------------------------------- 災害與時間：109.12.23豪雨災害 災點：11K+300上邊坡 災害編號：110-04-B11 施作項目：型框植生 完成施作時間：110.06 --------------------------------------------------------------- 災害與時間：111.10.10豪雨災害 災點：11K+200上邊坡 災害編號：111-04-B40 施作項目：型框植生612m2、縱洩(橫截)溝88m2 開始施作時間：111.11 完成施作時間：112.07 --------------------------------------------------------------- 災害與時間：113.04.03地震災害 災點：11K+150上邊坡 災害編號：113-04-B14 施作項目：刷坡1600m2、掛網及錨筋灌漿1600m2 開始施作時間：113.04 完成施作時間：113.10 --------------------------------------------------------------- 災害與時間：113.04.03地震災害 災點：11K+300上邊坡 災害編號：113-04-B14 施作項目：刷坡1500m2、型框植生1500m2 開始施作時間：113.04 完成施作時間：113.08 --------------------------------------------------------------- 災害與時間：114年11月鳳凰颱風豪雨災害 災點：10K+400上邊坡 災害編號：115-04-B01 施作項目：型框植生1211m2、懸眺步道修復135m 開始施作時間：115.06 完成施作時間：115.10</t>
+  </si>
+  <si>
+    <t>2026/10/17 下午 02:53:03</t>
   </si>
   <si>
     <t>0209DX-010800-D0-00-00000</t>
@@ -691,7 +691,7 @@
     <t>1. 邊坡有疑似不穩定徵兆 109年12月23日豪雨災害，造成下邊坡滑動，10.9k處路面下陷，擬設置微型樁加擋土牆，已於110年6月完工。 災害編號：110-04-B11 ----------------------------------------------------------------------- 2.邊坡現況良好115年1月滾動調整為D級。</t>
   </si>
   <si>
-    <t>2026/5/20 下午 03:37:23</t>
+    <t>2026/10/17 下午 02:58:24</t>
   </si>
   <si>
     <t>0209DX-011200-D0-00-00000</t>
@@ -715,7 +715,7 @@
     <t>山崩與地滑地質敏感區(111K+400~114K+000)。岩屑崩滑高敏感區(112K+050-112K+470)。落石高敏感區(112K+350-112K+950)。 ------------------------------------------------------------ 106年12月2日豪雨災害致114K+370下邊坡發生邊坡土石崩落，於107年完成。 災害編號 107-04-B04 ------------------------------------------------------------ 106年11月9日豪雨災害致114K+350發生邊坡土石崩落。 災害編號 106-04-B31 ------------------------------------------------------------ 107年11月9日豪雨災害造成11K+200下邊坡發生邊坡土石坍方已進行邊坡修復作業。上邊坡檔土牆護坡工程於108年4月完工。 ------------------------------------------------------------ 107年12月14日豪雨災害(台9丁線11K+200)路側沉陷，擬進行下邊坡擋土牆回填及邊坡掛網及錨筋灌漿，於108年5月完工。 災害編號108-04-B02 --------------------------------------------------------------------- 邊坡現況良好115年1月滾動調整為D級。</t>
   </si>
   <si>
-    <t>2026/5/20 下午 03:39:22</t>
+    <t>2026/10/17 下午 02:58:59</t>
   </si>
   <si>
     <t>0209DX-011400-A0-00-00000</t>
@@ -739,10 +739,10 @@
     <t>107/11(概估)</t>
   </si>
   <si>
-    <t>山崩地滑地質敏感區(114K+200-117K+100)。 ------------------------------------------------------------ 106年12月2日豪雨災害致114K+370上邊坡發生邊坡土石崩落，以錨定混凝土植生工程於107年完成。 災害編號 107-04-A01 ------------------------------------------------------------ 107年11月09日豪雨災害(台9丁線11K+800)上邊坡坍方，擬進行邊坡掛網及錨筋灌漿。 災害編號:107-04-B43 ---------------------------------------------------------------- ---------------------------------------------------- 災害與時間：114年11月鳳凰颱風豪雨災害 災點：11k+400 災害編號：115-04-B01 施作項目：型框植生1351m2 預計開始施作時間：115.6.30 預計完成施作時間：115.8.30</t>
-  </si>
-  <si>
-    <t>2026/5/20 下午 03:40:31</t>
+    <t>山崩地滑地質敏感區(114K+200-117K+100)。 ------------------------------------------------------------ 106年12月2日豪雨災害致114K+370上邊坡發生邊坡土石崩落，以錨定混凝土植生工程於107年完成。 災害編號 107-04-A01 ------------------------------------------------------------ 107年11月09日豪雨災害(台9丁線11K+800)上邊坡坍方，擬進行邊坡掛網及錨筋灌漿。 災害編號:107-04-B43 ---------------------------------------------------------------- ---------------------------------------------------- 災害與時間：114年11月鳳凰颱風豪雨災害 災點：11k+400 災害編號：115-04-B01 施作項目：型框植生1351m2 開始施作時間：115.6.30 完成施作時間：115.8.30</t>
+  </si>
+  <si>
+    <t>2026/10/16 上午 09:13:56</t>
   </si>
   <si>
     <t>0209DX-012200-A0-00-00000</t>
@@ -760,7 +760,7 @@
     <t>山崩與地滑地質敏感區(114K+200-117K+100)。岩屑崩滑高敏感區(115K+750~116K+000)。 --------------------------------------------------------------- 105年3月自然災害(115K+020)邊坡修復工程於106年4月完工。 災害編號:105-04-B23 --------------------------------------------------------------- 106年10月11日豪雨災害(115K+300-115K+328)。 災害編號:106-04-B25 --------------------------------------------------------------- 107年07月16日(台9丁線12K+500)上邊坡坍方，擬進行邊坡防落石柵工程。 災害編號:107-04-B27 --------------------------------------------------------------- 107年11月09日豪雨災害(台9丁線12K+500)路側擋土牆防落石柵損壞，擬進行修復。 災害編號:107-04-B43 --------------------------------------------------------------- 107年11月14日豪雨災害造成台9丁線12K+500上邊坡發生邊坡土石坍方已進行邊坡修復作業。上邊坡縱洩溝及噴凝土護坡工程於108年4月完工。 災害編號:107-04-B44 ---------------------------------------------------------------- 邊坡現況良好115年1月滾動調整為D級。</t>
   </si>
   <si>
-    <t>2026/5/20 下午 03:41:12</t>
+    <t>2026/10/17 下午 03:00:04</t>
   </si>
   <si>
     <t>0209DX-013000-D0-00-00000</t>
@@ -790,13 +790,13 @@
     <t>14k+500</t>
   </si>
   <si>
-    <t>自然邊坡,RC格框(格子梁),RC擋土牆,其他:型框植生、掛網、波崁磚擋土牆</t>
+    <t>自然邊坡,RC格框(格子梁),RC擋土牆,其他:型框植生、掛網、駁崁磚擋土牆</t>
   </si>
   <si>
     <t>第3級</t>
   </si>
   <si>
-    <t>1.10602豪雨災害 2.1071109豪雨災害 3.1071214豪雨災害 4.1071229坍方 5.1090607大型落石 6.11006坍方 7.1100915豪雨災害 8.11202豪雨災害 9.1131031康芮颱風</t>
+    <t>10602豪雨災害 1071109豪雨災害 1071214豪雨災害 1071229坍方 1090607大型落石 11006坍方 1100915豪雨災害 11202豪雨災害 1131031康芮颱風 115年3月5日豪雨災害</t>
   </si>
   <si>
     <t>106/02</t>
@@ -805,10 +805,10 @@
     <t>石牌公</t>
   </si>
   <si>
-    <t>1121023檢視發現邊坡範圍重複，將【台9丁線14K+000~14K+200】併入【台9丁線13K+200~14K+300】 ------------------------------------------------------------------ 山崩與地滑地質敏感區(114K+200~117K+100)。岩屑崩滑高敏感區(116K+780~116K+850)。邊坡無明顯不穩定徵兆。 ----------------------------------------------------------- 災害與時間：106年2月豪雨災害 災點：(舊樁號116K+500~116K+527)上邊坡 災害編號：1106-04-B06 已完成施作 ----------------------------------------------------------- 災害與時間：107.11.09豪雨災害 災點：13K+600上邊坡 災害編號：107-04-B43 施作項目：邊坡掛網及錨筋灌漿 完成施作時間：108.04 ----------------------------------------------------------- 災害與時間：107.12.14豪雨災害 災點：13K+650上邊坡 災害編號：108-04-B02 施作項目：掛網及錨筋灌漿 完成施作時間：108.04 ----------------------------------------------------------- 災害與時間：107.12.29豪雨災害 災點：14K+450上邊坡 災害編號：108-04-B05 施作項目：錨錠混凝土框 完成施作時間：108.05 ----------------------------------------------------------- 災害與時間：109.6.7豪雨災害 災點：13K+945上邊坡 災害編號：109-04-B12 施作項目：框型植生 完成施作時間：109.11 ----------------------------------------------------------- 災害與時間：110年6月豪雨災害 災點：14K+300上邊坡 災害編號：110-04-B20 施作項目：掛網護坡 開始施作時間：110.08 完成施作時間：110.08 ------------------------------------------------------------------ 災害與時間：110.09.15豪雨災害 災點：14K+100上邊坡 災害編號：110-04-B33 施作項目：掛網及錨筋灌漿3510m2 開始施作時間：111.10 完成施作時間：112.04 ----------------------------------------------------------- 災害與時間：112.02.08豪雨災害 災點：13K+600上邊坡 災害編號：112-04-B09 施作項目：刷坡1700m2、型框植生1700m2 開始施作時間：112.04 完成施作時間：112.07 ----------------------------------------------------------- 災害與時間：113.10.31康芮颱風 災點：13K+600上邊坡(重複致災) 災害編號：114-04-B01 施作項目：刷坡1400m2、型框植生1400m2 開始施作時間：114.02.10 完成施作時間：114.11.10 -----------------------------------------------------------------------</t>
-  </si>
-  <si>
-    <t>2026/10/5 下午 02:00:05</t>
+    <t>1121023檢視發現邊坡範圍重複，將【台9丁線14K+000~14K+200】併入【台9丁線13K+200~14K+300】 ----------------------------------------------------------- 山崩與地滑地質敏感區(114K+200~117K+100)。岩屑崩滑高敏感區(116K+780~116K+850)。邊坡無明顯不穩定徵兆。 ----------------------------------------------------------- 災害與時間：106年2月豪雨災害 災點：(舊樁號116K+500~116K+527)上邊坡 災害編號：1106-04-B06 已完成施作 ----------------------------------------------------------- 災害與時間：107.11.09豪雨災害 災點：13K+600上邊坡 災害編號：107-04-B43 施作項目：邊坡掛網及錨筋灌漿 完成施作時間：108.04 ----------------------------------------------------------- 災害與時間：107.12.14豪雨災害 災點：13K+650上邊坡 災害編號：108-04-B02 施作項目：掛網及錨筋灌漿 完成施作時間：108.04 ----------------------------------------------------------- 災害與時間：107.12.29豪雨災害 災點：14K+450上邊坡 災害編號：108-04-B05 施作項目：錨錠混凝土框 完成施作時間：108.05 ----------------------------------------------------------- 災害與時間：109.6.7豪雨災害 災點：13K+945上邊坡 災害編號：109-04-B12 施作項目：框型植生 完成施作時間：109.11 ----------------------------------------------------------- 災害與時間：110年6月豪雨災害 災點：14K+300上邊坡 災害編號：110-04-B20 施作項目：掛網護坡 開始施作時間：110.08 完成施作時間：110.08 ------------------------------------------------------------------ 災害與時間：110.09.15豪雨災害 災點：14K+100上邊坡 災害編號：110-04-B33 施作項目：掛網及錨筋灌漿3510m2 開始施作時間：111.10 完成施作時間：112.04 ----------------------------------------------------------- 災害與時間：112.02.08豪雨災害 災點：13K+600上邊坡 災害編號：112-04-B09 施作項目：刷坡1700m2、型框植生1700m2 開始施作時間：112.04 完成施作時間：112.07 ----------------------------------------------------------- 災害與時間：113.10.31康芮颱風 災點：13K+600上邊坡(重複致災) 災害編號：114-04-B01 施作項目：刷坡1400m2、型框植生1400m2 開始施作時間：114.02.10 完成施作時間：114.11.10 -------------------------------------------------------- 災害與時間：115.3.5豪雨災害 災點：14K+100上邊坡 災害編號：115-04-B02 施作項目：道路防落石(H)150m (W)60m 擋土牆工程、刷坡作業 開始施作時間：115.05.30 完成施作時間：115.07.30</t>
+  </si>
+  <si>
+    <t>2026/10/17 下午 02:12:25</t>
   </si>
   <si>
     <t>0209DX-013400-D0-00-00000</t>
@@ -835,7 +835,7 @@
     <t>邊坡無明顯不穩定徵兆 ----------------------------------------------------------- 109年2月20日(台9丁線13k+800)自然災害下邊坡坍方，進行擋土牆及噴凝土型框植生，於109年3月完工。災害編號109-04-B08 ----------------------------------------------------------- 邊坡現況良好115年1月滾動調整為D級。</t>
   </si>
   <si>
-    <t>2026/1/15 下午 04:53:24</t>
+    <t>2026/10/17 下午 03:00:41</t>
   </si>
   <si>
     <t>0209DX-013902-D0-00-00000</t>
@@ -883,7 +883,7 @@
     <t>110年6月豪雨災害，14K+250下邊坡出現蝕溝狀況，施做縱洩溝護坡(災編110-04-B20)，於110年8月開始施作，110年9月施作竣事。 ----------------------------------------------------------------------- 邊坡現況良好115年1月滾動調整為D級。</t>
   </si>
   <si>
-    <t>2026/5/20 下午 03:46:54</t>
+    <t>2026/10/17 下午 03:03:03</t>
   </si>
   <si>
     <t>0209DX-014800-A0-00-00000</t>
@@ -943,10 +943,10 @@
     <t>11010豪雨災害</t>
   </si>
   <si>
-    <t>110年10月13日豪雨災害，15K+750處上邊坡土石崩落，進行掛網及錨筋灌漿，於111年2月施作竣事。(災害編號：110-04-B37) ----------------------------------------------------------------</t>
-  </si>
-  <si>
-    <t>2026/10/8 下午 02:34:28</t>
+    <t>110年10月13日豪雨災害，15K+750處上邊坡土石崩落，進行掛網及錨筋灌漿，於111年2月施作竣事。(災害編號：110-04-B37) ---------------------------------------------------------------- 5年無重複致災，115年10月15日分級由C轉D級。</t>
+  </si>
+  <si>
+    <t>2026/10/17 下午 02:24:32</t>
   </si>
   <si>
     <t>0209DX-015600-D0-00-00000</t>
@@ -1123,7 +1123,7 @@
     <t>37k+170</t>
   </si>
   <si>
-    <t>自然邊坡,RC擋土牆,其他:型框植生、掛網、縱洩溝、堡崁磚擋土牆</t>
+    <t>自然邊坡,RC擋土牆,其他:型框植生、掛網、縱洩溝、駁崁磚擋土牆</t>
   </si>
   <si>
     <t>10409杜鵑風災 11010豪雨災害</t>
@@ -1138,7 +1138,7 @@
     <t>岩屑崩滑高敏感區(138K+000~139K+970)。山崩與地滑地質敏感區(138K+200~138K+400、138K+600~139K+000)。 ------------------------------------------------------------- 104年9月杜鵑風災坍方阻斷已完工(139K+400)。 ------------------------------------------------------------- 110年10月13日豪雨災害造成36K+300上邊坡土石坍方，施作縱洩溝，於111年3月完成施作(災害編號：110-04-B36) -------------------------------------------------------------- 現場植生狀況良好，115年1月調降為D級。</t>
   </si>
   <si>
-    <t>2026/1/15 下午 05:21:34</t>
+    <t>2026/10/14 下午 09:21:32</t>
   </si>
   <si>
     <t>0209DX-037170-A0-00-00000</t>
@@ -1150,19 +1150,19 @@
     <t>自然邊坡,噴凝土護坡,RC擋土牆,其他:框型植生、掛網</t>
   </si>
   <si>
-    <t>1051021豪雨災害 1070621豪雨災害 1080527豪雨災害 1091013豪雨災害 1091204豪雨災害 1100120豪雨災害 1120110豪雨災害 1140922樺加沙颱風</t>
+    <t>1051021豪雨災害 1070621豪雨災害 1080527豪雨災害 1091013豪雨災害 1091204豪雨災害 1100120豪雨災害 1120110豪雨災害 1140922樺加沙颱風 1150530豪雨災害</t>
   </si>
   <si>
     <t>109/12(概估)</t>
   </si>
   <si>
-    <t>落石高敏感區(139K+950~140K+550)。山崩與地滑地質敏感區(139K+200-140K+700)。 已納入105年10月21日豪雨災害(140.16k、140.4k、140.65k)，災害編號：105-04-A07。 107年6月21日豪雨災害造成(140K+200~140K+600)上邊坡發生邊坡土石坍方已進行邊坡修復作業。上邊坡掛網及錨筋灌漿護坡工程於108年4月完工(災害編號:107-04-B23)。 108年5月27日豪雨災害造成140K+620、140K+700路段發生邊坡土石坍落及邊坡滑動災害，進行邊坡掛網工程於108年10月完工。(災害編號:108-04-B18)。 109年10月13日豪雨災害37K+900上邊坡發生坍方，施做邊坡掛網及錨筋灌漿及噴植基材，於110年3月完工。(災害編號:109-04-B22) 109年12月04日豪雨災害37K+230上邊坡岩體破裂崩落，施做型框植生900m2，於110年月完工。(災害編號:110-04-B04) --------------------------------------------------------------- 災害與時間：110.01.20豪雨災害 災點：37K+600上邊坡 災害編號：110-04-B12 已修復竣事 ----------------------------------------------------------- 災害與時間：112.1.10豪雨災害 災點：37K+450上邊坡 災害編號：112-04-B06 施作項目：刷坡775m2、掛網及錨筋灌漿775m2、縱洩(橫截)溝48.6m2 開始施作時間：112.1 完成施作時間：112.08 ---------------------------------------------------- 災害與時間：114.09.22 災點：台9丁線37.8k 災害編號：114-04-B64 施作項目：邊坡掛網 開始施作時間：114.11 完成施作時間：115.1.5</t>
+    <t>落石高敏感區(139K+950~140K+550)。山崩與地滑地質敏感區(139K+200-140K+700)。 已納入105年10月21日豪雨災害(140.16k、140.4k、140.65k)，災害編號：105-04-A07。 107年6月21日豪雨災害造成(140K+200~140K+600)上邊坡發生邊坡土石坍方已進行邊坡修復作業。上邊坡掛網及錨筋灌漿護坡工程於108年4月完工(災害編號:107-04-B23)。 108年5月27日豪雨災害造成140K+620、140K+700路段發生邊坡土石坍落及邊坡滑動災害，進行邊坡掛網工程於108年10月完工。(災害編號:108-04-B18)。 109年10月13日豪雨災害37K+900上邊坡發生坍方，施做邊坡掛網及錨筋灌漿及噴植基材，於110年3月完工。(災害編號:109-04-B22) 109年12月04日豪雨災害37K+230上邊坡岩體破裂崩落，施做型框植生900m2，於110年月完工。(災害編號:110-04-B04) --------------------------------------------------------------- 災害與時間：110.01.20豪雨災害 災點：37K+600上邊坡 災害編號：110-04-B12 已修復竣事 ----------------------------------------------------------- 災害與時間：112.1.10豪雨災害 災點：37K+450上邊坡 災害編號：112-04-B06 施作項目：刷坡775m2、掛網及錨筋灌漿775m2、縱洩(橫截)溝48.6m2 開始施作時間：112.1 完成施作時間：112.08 ---------------------------------------------------- 災害與時間：114.09.22 災點：台9丁線37.8k 災害編號：114-04-B64 施作項目：邊坡掛網 開始施作時間：114.11 完成施作時間：115.1.5 ---------------------------------------------------- 災害與時間：114.05.30 災點：台9丁線37.7k 災害編號：115-04-B27 施作項目：防落石網搶修及型框植生搶修 開始施作時間：115.06.30 完成施作時間：115.09.19</t>
   </si>
   <si>
     <t>C1U850</t>
   </si>
   <si>
-    <t>2026/4/13 下午 01:32:10</t>
+    <t>2026/10/17 上午 08:41:33</t>
   </si>
   <si>
     <t>0209DX-037190-D0-00-00000</t>
@@ -1342,13 +1342,13 @@
     <t>自然邊坡,噴凝土護坡,其他:型框植生、掛網</t>
   </si>
   <si>
-    <t>11104豪雨災害</t>
+    <t>11104豪雨災害 1150530豪雨災害</t>
   </si>
   <si>
     <t>落石高敏感區(144K+950-145K+050)。山崩與地滑地質敏感區(140K+800-145K+200)。 ----------------------------------------------------------------- 111年4月3日豪雨災害42K+400上邊坡發生坍方，擬進行型框植生。(災害編號:111-04-B17)，於111年6月完成施工。</t>
   </si>
   <si>
-    <t>2026/1/15 下午 01:55:48</t>
+    <t>2026/10/17 上午 11:33:24</t>
   </si>
   <si>
     <t>0209DX-042500-D0-00-00000</t>
@@ -1378,16 +1378,16 @@
     <t>43k+550</t>
   </si>
   <si>
-    <t>1051021豪雨災害 1080930米塔颱風 1100120豪雨災害 1101013豪雨災害</t>
+    <t>1051021豪雨災害 1080930米塔颱風 1100120豪雨災害 1101013豪雨災害 1150530豪雨災害</t>
   </si>
   <si>
     <t>109/04</t>
   </si>
   <si>
-    <t>山崩與地滑地質敏感區(145K+400-146K+200)。上邊坡坍方進行預防性上邊坡掛網及錨筋灌漿護坡工程 --------------------------------------------------------------- 災害與時間：105.10.21豪雨災害 災點：(舊樁號146K+220) 災害編號：105-04-A07 已修復竣事 (146K+207~146K+227)。 上邊坡護坡工程業於107年1月完工。 --------------------------------------------------------------- 108年9月30日(米塔颱風災害)146K+300(9丁43K+500)上邊坡發生坍坊，進行邊坡掛網及錨筋灌漿，於109年3月完工。(災害編號:108-04-B35)。 --------------------------------------------------------------- 災害與時間：110.01.20豪雨災害 災點：43K+400上邊坡 災害編號：110-04-B12 已修復竣事 --------------------------------------------------------------- 110年10月13日豪雨災害，42K+700處上邊坡土石崩落，施作型框植生，於111年3月完成施作。(災害編號：110-04-B36) ------------------------------------------------------------</t>
-  </si>
-  <si>
-    <t>2023/5/24 下午 08:19:52</t>
+    <t>山崩與地滑地質敏感區(145K+400-146K+200)。上邊坡坍方進行預防性上邊坡掛網及錨筋灌漿護坡工程 --------------------------------------------------------------- 災害與時間：105.10.21豪雨災害 災點：(舊樁號146K+220) 災害編號：105-04-A07 已修復竣事 (146K+207~146K+227)。 上邊坡護坡工程業於107年1月完工。 --------------------------------------------------------------- 108年9月30日(米塔颱風災害)146K+300(9丁43K+500)上邊坡發生坍坊，進行邊坡掛網及錨筋灌漿，於109年3月完工。(災害編號:108-04-B35)。 --------------------------------------------------------------- 災害與時間：110.01.20豪雨災害 災點：43K+400上邊坡 災害編號：110-04-B12 已修復竣事 --------------------------------------------------------------- 110年10月13日豪雨災害，42K+700處上邊坡土石崩落，施作型框植生，於111年3月完成施作。(災害編號：110-04-B36) ------------------------------------------------------------ 115年5月30日豪雨災害 台9丁線42k+800上邊坡，施作防落石網搶修，於115年8月11日完成施作。(災害編號：115-04-B27)</t>
+  </si>
+  <si>
+    <t>2026/10/17 下午 03:17:13</t>
   </si>
   <si>
     <t>0209DX-043450-D0-00-00000</t>
@@ -1639,10 +1639,10 @@
     <t>106/08</t>
   </si>
   <si>
-    <t>山崩與地滑地質敏感區(149K+000-152K+800)。 ---------------------------------------------------- 110.11.10修正里程為台9丁線47K+795~48K+840。 ---------------------------------------------------- 災害與時間：105年9月梅姬颱風 災點：(150.85、150.95) 施作項目：縱洩溝護坡 完成施作時間：106年8月 ---------------------------------------------------- 災害與時間：113.04.03地震災害 災點：48K+815上邊坡 災害編號：113-04-B13 施作項目：防落石柵修復30m 開始施作時間：113.04 完成施作時間：</t>
-  </si>
-  <si>
-    <t>2026/9/24 上午 10:54:28</t>
+    <t>山崩與地滑地質敏感區(149K+000-152K+800)。 ---------------------------------------------------- 110.11.10修正里程為台9丁線47K+795~48K+840。 ---------------------------------------------------- 災害與時間：105年9月梅姬颱風 災點：(150.85、150.95) 施作項目：縱洩溝護坡 完成施作時間：106年8月 ---------------------------------------------------- 災害與時間：113.04.03地震災害 災點：48K+815上邊坡 災害編號：113-04-B13 施作項目：防落石柵修復30m 開始施作時間：113.04 完成施作時間：113.08.01</t>
+  </si>
+  <si>
+    <t>2026/10/16 上午 11:53:52</t>
   </si>
   <si>
     <t>0209DX-048840-A0-00-00000</t>
@@ -1750,13 +1750,13 @@
     <t>和中</t>
   </si>
   <si>
-    <t>山崩與地滑地質敏感區(162K+900-164K+800)。 --------------------------------------------------------------- 災害與時間：105 災點：(舊樁號164K+700)明隧道災害修復加固 災害編號：105-04-A04 已修復竣事 --------------------------------------------------------------- 災害與時間：105年7月尼伯特風災 災點：(163.95k、164.3k、164.45k) 災害編號：-- 已修復竣事(106年4月) -------------------------------------------------- 災害與時間：106年10月11日豪雨災害 災點：(164K+050-164K+250) 災害編號：106-04-B25 已修復竣事 -------------------------------------------------- 災害與時間：107年度豪大雨災害邊坡保護作業(107年2月6日地震、107年4月因強降豪大雨) 災點：(163K+950~164K+100)、(164K+200~164K+400) 災害編號：-- 已修復竣事 -------------------------------------------------- 災害與時間：107.09.15豪雨災害 災點：(164K+500上邊坡) 災害編號：107-04-B36 施作項目：刷坡30002、掛網及錨筋灌漿3000m2、H型鋼防石柵75m 開始施作時間：107.09 完成施作時間：108.03 ------------------------------------------------- 災害與時間：109.12.01豪雨災害 災點：61K+500上邊坡 災害編號：110-04-B06 施作項目：縱洩(橫截)溝2400m2 開始施作時間：110.02 完成施作時間：110.04 ------------------------------------------------------------ 災害與時間：110年10月12日豪雨災害 災點：62K+400上邊坡(明隧道) 災害編號：110-04-B23 施作項目：明隧道修補 開始施作時間：110.09.01 完成施作時間：111.08.24 ------------------------------------------------------------ 災害與時間：110年10月12日豪雨災害 災點：62K+400處上邊坡 災害編號：110-04-B39 施作項目：刷坡2108m2、掛網及錨筋灌漿2108m2 開始施作時間：110.09 完成施作時間：111.02 ------------------------------------------------------------ 災害與時間：110.12.12明隧道災害復健(擴充) 災點：62K+400上邊坡(明隧道) 災害編號：111-04-B02 施作項目：明隧道復建 開始施作時間：110.12.12 完成施作時間：111.08.24 ------------------------------------------------------------ 災害與時間：111年3月25日豪雨災害 災點：61K+300處上邊坡 災害編號：111-04-B14 施作項目：掛網及錨筋灌漿2700m2 開始施作時間：111.03 完成施作時間：111.07 --------------------------------------------------------------- 災害與時間：111.09老舊復建作業 災點：61K+750上邊坡(明隧道) 災害編號：111-04-A03 施作項目：明隧道老舊復建 開始施作時間：111.11 完成施作時間：112.05 --------------------------------------------------------------- 災害與時間：111.10.10豪雨災害 災點：61K+300上邊坡 災害編號：111-04-B44 施作項目：掛網及錨筋灌漿104m2 開始施作時間：111.11 完成施作時間：112.05 --------------------------------------------------------------- 災害與時間：111.10.10豪雨災害 災點：61K+350上邊坡 災害編號：111-04-B44 施作項目：掛網及錨筋灌漿2800m2 開始施作時間：111.11 完成施作時間：112.02 --------------------------------------------------------------- 災害與時間：111.10.31豪雨災害 災點：61K+310上邊坡 災害編號：111-04-B39 施作項目：刷坡580m2、噴凝土580m2 開始施作時間：111.12 完成施作時間：112.05 ---------------------------------------------------- 災害與時間：114.05.20豪雨災害 災點：61.2、61.3、61.5上邊坡 災害編號：114-04-B37 施作項目：縱洩溝 開始施作時間：114.7.1 完成施作時間：115.01.15 ---------------------------------------------------- 災害與時間：114.7.6丹娜絲颱風災害 災點：61.2~61.550k 災害編號：114-04-A23, 114-04-B59 施作項目：簾幕式防落石網(設計中) 開始施作時間：設計中 完成施作時間：設計中</t>
+    <t>山崩與地滑地質敏感區(162K+900-164K+800)。 --------------------------------------------------------------- 災害與時間：105 災點：(舊樁號164K+700)明隧道災害修復加固 災害編號：105-04-A04 已修復竣事 --------------------------------------------------------------- 災害與時間：105年7月尼伯特風災 災點：(163.95k、164.3k、164.45k) 災害編號：-- 已修復竣事(106年4月) -------------------------------------------------- 災害與時間：106年10月11日豪雨災害 災點：(164K+050-164K+250) 災害編號：106-04-B25 已修復竣事 -------------------------------------------------- 災害與時間：107年度豪大雨災害邊坡保護作業(107年2月6日地震、107年4月因強降豪大雨) 災點：(163K+950~164K+100)、(164K+200~164K+400) 災害編號：-- 已修復竣事 -------------------------------------------------- 災害與時間：107.09.15豪雨災害 災點：(164K+500上邊坡) 災害編號：107-04-B36 施作項目：刷坡30002、掛網及錨筋灌漿3000m2、H型鋼防石柵75m 開始施作時間：107.09 完成施作時間：108.03 ------------------------------------------------- 災害與時間：109.12.01豪雨災害 災點：61K+500上邊坡 災害編號：110-04-B06 施作項目：縱洩(橫截)溝2400m2 開始施作時間：110.02 完成施作時間：110.04 ------------------------------------------------------------ 災害與時間：110年10月12日豪雨災害 災點：62K+400上邊坡(明隧道) 災害編號：110-04-B23 施作項目：明隧道修補 開始施作時間：110.09.01 完成施作時間：111.08.24 ------------------------------------------------------------ 災害與時間：110年10月12日豪雨災害 災點：62K+400處上邊坡 災害編號：110-04-B39 施作項目：刷坡2108m2、掛網及錨筋灌漿2108m2 開始施作時間：110.09 完成施作時間：111.02 ------------------------------------------------------------ 災害與時間：110.12.12明隧道災害復健(擴充) 災點：62K+400上邊坡(明隧道) 災害編號：111-04-B02 施作項目：明隧道復建 開始施作時間：110.12.12 完成施作時間：111.08.24 ------------------------------------------------------------ 災害與時間：111年3月25日豪雨災害 災點：61K+300處上邊坡 災害編號：111-04-B14 施作項目：掛網及錨筋灌漿2700m2 開始施作時間：111.03 完成施作時間：111.07 --------------------------------------------------------------- 災害與時間：111.09老舊復建作業 災點：61K+750上邊坡(明隧道) 災害編號：111-04-A03 施作項目：明隧道老舊復建 開始施作時間：111.11 完成施作時間：112.05 --------------------------------------------------------------- 災害與時間：111.10.10豪雨災害 災點：61K+300上邊坡 災害編號：111-04-B44 施作項目：掛網及錨筋灌漿104m2 開始施作時間：111.11 完成施作時間：112.05 --------------------------------------------------------------- 災害與時間：111.10.10豪雨災害 災點：61K+350上邊坡 災害編號：111-04-B44 施作項目：掛網及錨筋灌漿2800m2 開始施作時間：111.11 完成施作時間：112.02 --------------------------------------------------------------- 災害與時間：111.10.31豪雨災害 災點：61K+310上邊坡 災害編號：111-04-B39 施作項目：刷坡580m2、噴凝土580m2 開始施作時間：111.12 完成施作時間：112.05 ---------------------------------------------------- 災害與時間：114.05.20豪雨災害 災點：61.2、61.3、61.5上邊坡 災害編號：114-04-B37 施作項目：縱洩溝 開始施作時間：114.7.1 完成施作時間：115.01.15 ---------------------------------------------------- 災害與時間：114.7.6丹娜絲颱風災害 災點：61.2~61.550k 災害編號：114-04-A23, 114-04-B59 施作項目：簾幕式防落石網 開始施作時間：115.07.07 完成施作時間：施工中</t>
   </si>
   <si>
     <t>C0T9D0</t>
   </si>
   <si>
-    <t>2026/5/23 上午 09:39:39</t>
+    <t>2026/10/13 上午 08:38:00</t>
   </si>
   <si>
     <t>0209DX-061250-D0-00-00000</t>
@@ -2221,7 +2221,7 @@
     <t>121k+300</t>
   </si>
   <si>
-    <t>自然邊坡,噴凝土護坡,RC擋土牆,其他:掛網、型框植生、砌石擋土牆、波崁磚擋土牆</t>
+    <t>自然邊坡,噴凝土護坡,RC擋土牆,其他:掛網、型框植生、砌石擋土牆、駁崁磚擋土牆</t>
   </si>
   <si>
     <t>108年9月30日米塔颱風</t>
@@ -2233,7 +2233,7 @@
     <t>106年9月完工(128K+100-128K+110)。 108年9月30日一般災害(米塔胎風災害)121K+300上邊坡發生坍方，進行型框植生工程，於109年2月底完工。(災害編號:108-04-B35)。 ------------------------------------------------------------------------- 現場植生狀況良好，115年1月調降為D級。</t>
   </si>
   <si>
-    <t>2026/1/15 下午 05:33:12</t>
+    <t>2026/10/14 下午 09:22:06</t>
   </si>
   <si>
     <t>0209X-121900-A0-00-00000</t>
@@ -2287,16 +2287,16 @@
     <t>第5級</t>
   </si>
   <si>
-    <t>108年5月24日豪雨災害 108年8月24日豪雨災害 11110豪雨災害 1130403地震災害 1140509及18日豪雨</t>
+    <t>108年5月24日豪雨災害 108年8月24日豪雨災害 11110豪雨災害 1130403地震災害 1140509及18日豪雨 1150425豪雨災害</t>
   </si>
   <si>
     <t>和平</t>
   </si>
   <si>
-    <t>災害與時間：108.05.24豪雨災害 災點：(159K+700)上邊坡 災害編號：108-04-B16 施作項目：H型鋼防石柵10m 開始施作時間：108.05 完成施作時間：108.12 ---------------------------------------------------- 災害與時間：108.08.24豪雨災害 災點：(159K+910)上邊坡 災害編號：108-04-B24 施作項目：H型鋼防石柵10m 開始施作時間：108.08 完成施作時間：108.12 ---------------------------------------------------- 災害與時間：111.10.17豪雨災害 災點：148K+200上邊坡 災害編號：111-04-B44 施作項目：噴凝土1680m2 開始施作時間：111.11 完成施作時間：112.05 ---------------------------------------------------- 災害與時間：113.04.03地震災害 災點：147K+700~148K+200上邊坡 災害編號：113-04-A13 施作項目：簾幕式防落石網 開始施作時間：113.07.01 完成施作時間：114.04.10 ------------------------------------------------------------------- 災害與時間：114.5.9豪雨災害, 114.5.18豪雨災害 災點：147.5k、147.7k 災害編號：113-04-A13, 113-04-A25, 114-04-B36 施作項目：型框植生 開始施作時間：113.5.30 完成施作時間：114.6.30 ---------------------------------------------------- 災害與時間：113年9月山陀兒颱風 災點：146K+900 災害編號：114-04-B11 施作項目：型框植生護坡 開始施作時間：114.03.03 完成施作時間：114.03.31 ------------------------------------------------------------------- 災害與時間：114.7.6丹娜絲颱風災害 災點：147.1k 災害編號：114-04-B59 施作項目：型框植生 開始施作時間：114.10.27 完成施作時間：114.12.22</t>
-  </si>
-  <si>
-    <t>2026/5/23 上午 09:55:45</t>
+    <t>災害與時間：108.05.24豪雨災害 災點：(159K+700)上邊坡 災害編號：108-04-B16 施作項目：H型鋼防石柵10m 開始施作時間：108.05 完成施作時間：108.12 ---------------------------------------------------- 災害與時間：108.08.24豪雨災害 災點：(159K+910)上邊坡 災害編號：108-04-B24 施作項目：H型鋼防石柵10m 開始施作時間：108.08 完成施作時間：108.12 ---------------------------------------------------- 災害與時間：111.10.17豪雨災害 災點：148K+200上邊坡 災害編號：111-04-B44 施作項目：噴凝土1680m2 開始施作時間：111.11 完成施作時間：112.05 ---------------------------------------------------- 災害與時間：113.04.03地震災害 災點：147K+700~148K+200上邊坡 災害編號：113-04-A13 施作項目：簾幕式防落石網 開始施作時間：113.07.01 完成施作時間：114.04.10 ------------------------------------------------------------------- 災害與時間：114.5.9豪雨災害, 114.5.18豪雨災害 災點：147.5k、147.7k 災害編號：113-04-A13, 113-04-A25, 114-04-B36 施作項目：型框植生 開始施作時間：113.5.30 完成施作時間：114.6.30 ---------------------------------------------------- 災害與時間：113年9月山陀兒颱風 災點：146K+900 災害編號：114-04-B11 施作項目：型框植生護坡 開始施作時間：114.03.03 完成施作時間：114.03.31 ------------------------------------------------------------------- 災害與時間：114.7.6丹娜絲颱風災害 災點：147.1k 災害編號：114-04-B59 施作項目：型框植生 開始施作時間：114.10.27 完成施作時間：114.12.22 -----------------------------------------------------------------------災害與時間：115.04.25豪雨災害 災點：147.7k 災害編號：115-04-A14 施作項目：型框植生+縱洩溝 開始施作時間：115.07.30 完成施作時間：施工中 -----------------------------------------------------------------------</t>
+  </si>
+  <si>
+    <t>2026/10/16 下午 01:32:50</t>
   </si>
   <si>
     <t>0209X-158195-A0-00-00000</t>
@@ -2308,10 +2308,10 @@
     <t>158k+600</t>
   </si>
   <si>
-    <t>防石柵,噴凝土護坡,岩(地)錨(格梁),其他:掛網、型框植生、縱洩溝、攔砂壩、明隧道、砌石護坡</t>
-  </si>
-  <si>
-    <t>105年9月梅姬颱風 107年9月15日豪雨災害 108年2月4日豪雨災害 108年8月24日豪雨災害 1130403地震災害</t>
+    <t>防石柵,RC擋土牆,其他:掛網、型框植生、縱洩溝、攔砂壩、明隧道、砌石護坡</t>
+  </si>
+  <si>
+    <t>105年9月梅姬颱風 107年9月15日豪雨災害 108年2月4日豪雨災害 108年8月24日豪雨災害 1130403地震災害 113.7月凱米颱風</t>
   </si>
   <si>
     <t>105/09(概估)</t>
@@ -2323,7 +2323,7 @@
     <t>落石高敏感區(170K+550~171K+550)。 山崩地滑地質敏感區(173K+300~174K+400)。 ---------------------------------------------------- 災害與時間：105年9月梅姬颱風 災點：(171k+150，171k+700~+820) 施作項目：掛網及錨筋灌漿護坡 完成施作時間：106.11 ---------------------------------------------------- 災害與時間： 107年9月15日豪雨災害 災點：(171K+300、171K+100) 災害編號：107-04-B36 施作項目：掛網及錨筋灌漿、噴凝土護坡 完成施作時間：108.04 ---------------------------------------------------- 災害與時間： 108年2月4日豪雨災害 災點：(171K+960上邊坡) 災害編號：108-04-B06 施作項目：掛網及錨筋灌漿護坡工程 完成施作時間：108.7.22 ---------------------------------------------------- 災害與時間：108年8月24日豪雨災害 災點：(171K+960上邊坡) 災害編號：108-04-B24 施作項目：防石柵用H型鋼 完成施作時間：108.12 ---------------------------------------------------- 災害與時間：113.07月凱米颱風災害 災點：158K+600上邊坡 災害編號：113-04-A21 施作項目：簾幕式防護網 開始施作時間：114.6.16 完成施作時間：115.01.21 ------------------------------------------------- 災害與時間：0403地震災害, 113.7月凱米颱風 災點：158K+300上邊坡 災害編號：114-04-A04, 114-04-A13 施作項目：防落石柵及邊坡掛網與灌漿錨筋, 簾幕式落石防護網 開始施作時間：113.8.16 完成施作時間：114.1.22 ----------------------------------------------------</t>
   </si>
   <si>
-    <t>2026/5/23 上午 10:36:04</t>
+    <t>2026/10/17 下午 12:59:15</t>
   </si>
   <si>
     <t>0209X-158600-A0-00-00000</t>
@@ -2332,10 +2332,10 @@
     <t>160k+330</t>
   </si>
   <si>
-    <t>自然邊坡,噴凝土護坡,其他:掛網、明隧道</t>
-  </si>
-  <si>
-    <t>107年7月納入明隧道新建工程 1120111豪雨災害 1130403地震災害</t>
+    <t>自然邊坡,其他:掛網、明隧道</t>
+  </si>
+  <si>
+    <t>107年7月納入明隧道新建工程 1120111豪雨災害 1130403地震災害 114年7月6日丹娜絲颱風 115.0425豪雨災害</t>
   </si>
   <si>
     <t>107/07</t>
@@ -2344,10 +2344,10 @@
     <t>大清水隧道及錦文隧道</t>
   </si>
   <si>
-    <t>山崩與地滑地質敏感區(167K+300-173K+400)。落石高敏感區：172K+500-174K+200。岩屑崩滑高敏感區：173K+700-174K+100。邊坡無明顯不穩定徵兆。 ---------------------------------------------------- 110.11.10 台9線158.6k~159.2k、159.3~160.3兩區段為大清水隧道及錦文隧道開口處，現皆已設置明隧道保護，併入158.6k~159.2k並加長匡列 全隧道區段(台9線158K+600~160K+330)。 ---------------------------------------------------- 災害與時間：107年7月(172K+700)納入明隧道新建工程 災點：(172K+700) 完成施作時間：109年3月31日 ---------------------------------------------------- 災害與時間：112.1.11豪雨災害 災點：159K+300上邊坡 災害編號：112-04-A04、A05、B05 施作項目：縱洩溝1159m2、掛網213m2、明隧道復建 開始施作時間：112.1 完成施作時間：112.12 ---------------------------------------------------- 災害與時間：0403地震, 114年7月6日丹娜絲颱風 災點：159K+400明隧道 災害編號：114-04-B07、114-04-B59 施作項目：明隧道頂板復建 開始施作時間：114.11.01 完成施作時間：115.04.30 ---------------------------------------------------- 災害與時間：113年10月31日康芮颱風 災點：159K+400上邊坡 災害編號：114-04-A16 施作項目：邊坡土石清理及掛網護坡 開始施作時間：114.03.03 完成施作時間：114.09.01 ----------------------------------------------------</t>
-  </si>
-  <si>
-    <t>2026/5/23 下午 03:17:45</t>
+    <t>山崩與地滑地質敏感區(167K+300-173K+400)。落石高敏感區：172K+500-174K+200。岩屑崩滑高敏感區：173K+700-174K+100。邊坡無明顯不穩定徵兆。 ---------------------------------------------------- 110.11.10 台9線158.6k~159.2k、159.3~160.3兩區段為大清水隧道及錦文隧道開口處，現皆已設置明隧道保護，併入158.6k~159.2k並加長匡列 全隧道區段(台9線158K+600~160K+330)。 ---------------------------------------------------- 災害與時間：107年7月(172K+700)納入明隧道新建工程 災點：(172K+700) 完成施作時間：109年3月31日 ---------------------------------------------------- 災害與時間：112.1.11豪雨災害 災點：159K+300上邊坡 災害編號：112-04-A04、A05、B05 施作項目：縱洩溝1159m2、掛網213m2、明隧道復建 開始施作時間：112.1 完成施作時間：112.12 ---------------------------------------------------- 災害與時間：0403地震, 114年7月6日丹娜絲颱風 災點：159K+400明隧道 災害編號：114-04-B07、114-04-B59 施作項目：明隧道頂板復建 開始施作時間：114.11.01 完成施作時間：施工中(預定115.11.30竣工) ---------------------------------------------------- 災害與時間：113年10月31日康芮颱風 災點：159K+400上邊坡 災害編號：114-04-A16 施作項目：邊坡土石清理及掛網護坡 開始施作時間：114.03.03 完成施作時間：114.09.01 ---------------------------------------------------- 災害與時間：115年4月25日豪雨災害 災點：159K+200上邊坡 災害編號：115-04-A10 施作項目：簾幕式防落石網及委託測量設計及監造 開始施作時間：預定115.11.10(設計中未施作) 完成施作時間：(設計中未施作) -----------------------------------------------------------------------</t>
+  </si>
+  <si>
+    <t>2026/10/17 下午 12:17:17</t>
   </si>
   <si>
     <t>0209X-160330-A0-00-00000</t>
@@ -2356,16 +2356,16 @@
     <t>160k+900</t>
   </si>
   <si>
-    <t>自然邊坡,防石柵,噴凝土護坡,其他:掛網</t>
-  </si>
-  <si>
-    <t>106年度11月完工 10912豪雨災害 11005自然災害 11009一般災害 11010豪雨災害 1130403地震災害</t>
+    <t>自然邊坡,防石柵,其他:掛網</t>
+  </si>
+  <si>
+    <t>106年度11月完工 10912豪雨災害 11005自然災害 11009一般災害 11010豪雨災害 1130403地震災害 114.5.9豪雨災害 114.5.18豪雨災害 113年7月凱米颱風 114.07.06丹娜絲颱風</t>
   </si>
   <si>
     <t>落石高敏感區(172K+500-174K+200)。岩屑崩滑高敏感區(173K+700-174K+100)。 ---------------------------------------------------- 災害與時間：106年坍方 災點：(174K+300~174K+320) 施作項目：掛網修復 完成施作時間：106.11 ---------------------------------------------------- 災害與時間：109年12月豪雨 災點：160K+400上邊坡 災害編號：110-04-B06 施作項目：掛網及錨筋灌漿 完成施作時間：110年5月31日 ---------------------------------------------------- 災害與時間：110年5月自然災害 災點：160.7K上邊坡 施作項目：掛網及錨筋灌漿 災害編號：110-04-B18 開始施作時間：11007 完成施作時間：已修復竣事 ---------------------------------------------------- 災害與時間：110.09.13一般災害 災點：160K+700上邊坡 災害編號：110-04-B30 完成施作時間：已修復竣事 ---------------------------------------------------- 災害與時間：110年10月12日豪雨災害 災點：160K+550處上邊坡 災害編號：110-04-B39 施作項目：掛網及錨筋灌漿、防石柵、縱洩溝 完成施作時間：110年12月 ---------------------------------------------------- 災害與時間：113.04.03地震災害, 113年7月凱米颱風 災點：160K+700上邊坡 災害編號：(113-04-A13, 113-04-A25) 施作項目：(格梁護坡, 噴植法植生護坡) 開始施作時間：113.6.1 完成施作時間：113.9.15 ---------------------------------------------------- 災害與時間:113.04.03地震災害, 114.5.9及114.5.18豪雨災害, 113年7月凱米颱風 災點：160K+800上邊坡 災害編號：113-04-A13, 114-04-B36, 114-04-B59 施作項目：格梁護坡, 噴植法植生護坡 開始施作時間：113.7.1 完成施作時間：113.9.15 ---------------------------------------------------- 災害與時間：114.07.06丹娜絲颱風災害 災點：160K+900上邊坡 災害編號：114-04-B37, 114-04-B59 施作項目：框型植生 開始施作時間：114.11.01 完成施作時間：115.01.15</t>
   </si>
   <si>
-    <t>2026/5/23 上午 10:51:28</t>
+    <t>2026/10/17 下午 12:59:56</t>
   </si>
   <si>
     <t>0209X-160800-D0-00-00000</t>
@@ -2395,16 +2395,16 @@
     <t>自然邊坡,防石柵,噴凝土護坡,其他:掛網、型框植生</t>
   </si>
   <si>
-    <t>10808豪雨災害 11010豪雨災害 1130403地震災害 1140330豪雨災害 1140719薇帕颱風</t>
+    <t>10808豪雨災害 11010豪雨災害 1130403地震災害 1140330豪雨災害 1140719薇帕颱風 1150425豪雨災害 1150709巴威颱風</t>
   </si>
   <si>
     <t>108/08(概估)</t>
   </si>
   <si>
-    <t>---------------------------------------------------- 災害與時間：108年8月24日豪雨災害 災點：(台9線174k+460、174K+500及174K+550上邊坡) 災害編號：108-04-B24 施作項目：防石柵用H型鋼 完成施作時間：109.09 ---------------------------------------------------- 災害與時間：110年10月12日豪雨災害 災點：161K+100處上邊坡 災害編號：110-04-B39 施作項目：掛網及錨筋灌漿、型框植生 完成施作時間：111.02 ---------------------------------------------------- 災害與時間：113.04.03地震災害, 113年7月凱米颱風 災點：161K+200上邊坡 災害編號：113-04-A13, 113-04-A25 施作項目：格梁護坡, 掛網、縱洩溝、型框植生 開始施作時間：113.7.10 完成施作時間：113.9.15 ---------------------------------------------------- 災害與時間：114年7月19日薇帕颱風, 114.05.09豪雨災害, 114.05.18豪雨災害 災點：161.300, 161.350 災害編號：114-04-A23, 114-04-B36, 114-04-B43 施作項目：型框植生護坡、縱洩溝、橫截溝、噴植生基材 開始施作時間：114.07.19 預定完成施作時間：114.01.15 ---------------------------------------------------- 災害與時間：114.7.19薇帕颱風災害 災點：161.1 災害編號：114-04-B43 施作項目：型框植生 開始施作時間：114.7.19 預定完成施作時間：115.01.15 ---------------------------------------------------- 災害與時間：114.7.19薇帕颱風災害 災點：161.150 災害編號：114-04-B43 施作項目：縱洩溝 開始施作時間：113.11.15 預定完成施作時間：114.04.25 ---------------------------------------------------- 災害與時間：113年10月31日康芮颱風 災點：161.070 災害編號：114-04-B18 施作項目：縱洩溝及橫截溝 開始施作時間：114.10.20 預定完成施作時間：115.01.15</t>
-  </si>
-  <si>
-    <t>2026/1/15 下午 05:33:29</t>
+    <t>---------------------------------------------------- 災害與時間：108年8月24日豪雨災害 災點：(台9線174k+460、174K+500及174K+550上邊坡) 災害編號：108-04-B24 施作項目：防石柵用H型鋼 完成施作時間：109.09 ---------------------------------------------------- 災害與時間：110年10月12日豪雨災害 災點：161K+100處上邊坡 災害編號：110-04-B39 施作項目：掛網及錨筋灌漿、型框植生 完成施作時間：111.02 ---------------------------------------------------- 災害與時間：113.04.03地震災害, 113年7月凱米颱風 災點：161K+200上邊坡 災害編號：113-04-A13, 113-04-A25 施作項目：格梁護坡, 掛網、縱洩溝、型框植生 開始施作時間：113.7.10 完成施作時間：113.9.15 ---------------------------------------------------- 災害與時間：114年7月19日薇帕颱風, 114.05.09豪雨災害, 114.05.18豪雨災害 災點：161.300, 161.350 災害編號：114-04-A23, 114-04-B36, 114-04-B43 施作項目：型框植生護坡、縱洩溝、橫截溝、噴植生基材 開始施作時間：114.07.19 預定完成施作時間：114.01.15 ---------------------------------------------------- 災害與時間：114.7.19薇帕颱風災害 災點：161.1 災害編號：114-04-B43 施作項目：型框植生 開始施作時間：114.7.19 預定完成施作時間：115.01.15 ---------------------------------------------------- 災害與時間：114.7.19薇帕颱風災害 災點：161.150 災害編號：114-04-B43 施作項目：縱洩溝 開始施作時間：113.11.15 預定完成施作時間：114.04.25 ---------------------------------------------------- 災害與時間：113年10月31日康芮颱風 災點：161.070 災害編號：114-04-B18 施作項目：縱洩溝及橫截溝 開始施作時間：114.10.20 預定完成施作時間：115.01.15 ----------------------------------------------------------------------- 災害與時間：115年04月25日豪雨災害 災點：161K+200 災害編號：115-04-B23 施作項目：型鋼防落石柵搶修 開始施作時間：預定115.11.10(設計中未施作) 預定完成施作時間：(設計中未施作) ----------------------------------------------------------------------- 災害與時間：115年7月9日巴威颱風 災點：161.350 災害編號：115-04-B54 施作項目：形框植生護坡 開始施作時間：115.9.01 預定完成施作時間：115.10.05 -----------------------------------------------------------------------</t>
+  </si>
+  <si>
+    <t>2026/10/17 上午 11:42:31</t>
   </si>
   <si>
     <t>0209X-162650-A0-00-00000</t>
@@ -2422,10 +2422,10 @@
     <t>10901一般災害 11005自然災害 11103豪雨災害 1130403地震災害 1140520豪雨災害</t>
   </si>
   <si>
-    <t>落石高敏感區(175K+950-177K+500)。山崩與地滑地質敏感區(175K+400-181K+000)。 ---------------------------------------------------- 災害與時間：109年1月一般災害 災點：162K+850上邊坡 災害編號：109-04-B01 施作項目：掛網及錨筋灌漿面積計2496m2 完成施作時間：109.06 ---------------------------------------------------- 災害與時間：109年1月一般災害 災點：162K+950上邊坡 災害編號：109-04-B01 施作項目：邊坡掛網及錨筋灌漿面積計539m2 完成施作時間：109.06 ------------------------------------------------------------- 災害與時間：110.05.05自然災害 災點：162K+700上邊坡 災害編號：110-04-B18 已修復竣事 ---------------------------------------------------- 災害與時間：111年3月豪雨災害 災點：162K+700上邊坡 災害編號：111-04-B14 施作項目：邊坡掛網及錨筋灌漿面積計2636m2 完成施作時間：111.07 ---------------------------------------------------- 災害與時間：113.04.03地震災害 災點：162K+800上邊坡 災害編號：(114-04-A19) 施作項目：簾幕式防護網 開始施作時間：114.12.01 完成施作時間：115.06.05 ---------------------------------------------------- 災害與時間：0403地震災害 災點：162.9k 災害編號：114-04-B08 施作項目：邊坡掛網噴漿 開始施作時間：114.12.01 完成施作時間：115.06.05 ---------------------------------------------------- 災害與時間：0403地震災害 災點：162.750-900k 災害編號：114-04-A19 施作項目：明隧道工程 開始施作時間：114.12.01 完成施作時間：115.06.05 ----------------------------------------------------</t>
-  </si>
-  <si>
-    <t>2026/5/23 上午 11:32:33</t>
+    <t>落石高敏感區(175K+950-177K+500)。山崩與地滑地質敏感區(175K+400-181K+000)。 ---------------------------------------------------- 災害與時間：109年1月一般災害 災點：162K+850上邊坡 災害編號：109-04-B01 施作項目：掛網及錨筋灌漿面積計2496m2 完成施作時間：109.06 ---------------------------------------------------- 災害與時間：109年1月一般災害 災點：162K+950上邊坡 災害編號：109-04-B01 施作項目：邊坡掛網及錨筋灌漿面積計539m2 完成施作時間：109.06 ------------------------------------------------------------- 災害與時間：110.05.05自然災害 災點：162K+700上邊坡 災害編號：110-04-B18 已修復竣事 ---------------------------------------------------- 災害與時間：111年3月豪雨災害 災點：162K+700上邊坡 災害編號：111-04-B14 施作項目：邊坡掛網及錨筋灌漿面積計2636m2 完成施作時間：111.07 ---------------------------------------------------- 災害與時間：113.04.03地震災害 災點：162K+800上邊坡 災害編號：(114-04-A19) 施作項目：簾幕式防護網 開始施作時間：114.12.01 完成施作時間：115.06.05 ---------------------------------------------------- 災害與時間：0403地震災害 災點：162.9k 災害編號：114-04-B08 施作項目：邊坡掛網噴漿 開始施作時間：114.12.01 完成施作時間：115.06.05 ---------------------------------------------------- 災害與時間：0403地震災害 災點：162.750-900k 災害編號：114-04-A19 施作項目：明隧道工程 開始施作時間：115.8.13 完成施作時間：施工中 ----------------------------------------------------</t>
+  </si>
+  <si>
+    <t>2026/10/17 上午 11:41:03</t>
   </si>
   <si>
     <t>0209X-163300-A0-00-00000</t>
@@ -2443,10 +2443,10 @@
     <t>1130403地震災害 114.07.06丹娜絲颱風 115.4.25 豪雨災害 台9線163k+300水溝</t>
   </si>
   <si>
-    <t>落石高敏感區：175K+950-177K+500。山崩地滑地質敏感區(175K+400~181K+000)。 ---------------------------------------------------- 災害與時間：0403地震災害, 114年07日凱米颱風 災點：163K+400上邊坡 災害編號：114-04-A13, 114-04-A25 施作項目：格梁護坡, 噴植法植生護坡 開始施作時間：114.09.30 完成施作時間：114.01.22 -------------------------------------------------------- 災害與時間：114.07.06丹娜絲颱風 災點：崇德隧道南、北口163K~163K+400 災害編號：114-04-A24 施作項目：防護牆施作 開始施作時間：115.01.31 完成施作時間：115.05.31</t>
-  </si>
-  <si>
-    <t>2026/10/12 上午 11:13:05</t>
+    <t>落石高敏感區：175K+950-177K+500。山崩地滑地質敏感區(175K+400~181K+000)。 ---------------------------------------------------- 災害與時間：0403地震災害, 114年07日凱米颱風 災點：163K+400上邊坡 災害編號：114-04-A13, 114-04-A25 施作項目：格梁護坡, 噴植法植生護坡 開始施作時間：114.09.30 完成施作時間：114.01.22 -------------------------------------------------------- 災害與時間：114.07.06丹娜絲颱風 災點：崇德隧道南、北口163K~163K+400 災害編號：114-04-A24 施作項目：防護牆施作 開始施作時間：115.09.01 完成施作時間：施工中 ----------------------------------------------------------------------- 災害與時間：115.04.25豪雨災害 災點：163K+300 災害編號：115-04-B23 施作項目：水溝修繕 開始施作時間：115.04.20 完成施作時間：115.04.22 -----------------------------------------------------------------------</t>
+  </si>
+  <si>
+    <t>2026/10/17 上午 11:37:28</t>
   </si>
   <si>
     <t>0209X-163710-A0-00-00000</t>
@@ -2458,7 +2458,7 @@
     <t>164k+050</t>
   </si>
   <si>
-    <t>自然邊坡,噴凝土護坡,其他:縱洩溝</t>
+    <t>自然邊坡,其他:縱洩溝</t>
   </si>
   <si>
     <t>10507尼伯特風災 1130724凱米颱風</t>
@@ -2467,7 +2467,7 @@
     <t>落石高敏感區：175K+950-177K+500。山崩與地滑地質敏感區(175K+400-181K+000)。已納入105年7月尼伯特風災修復工程於106年4月完成。 --------------------------------------------------------------- 五年內無災害紀錄，奉本處四工養字第1110087350號 辦理調整至D級。 ---------------------------------------------------- 災害與時間：113.10.30康芮颱風 災點：台9線163K+950、163K+900 災害編號：114-04-B18, 114-04-B37 施作項目：型框植生及縱洩溝 開始施作時間：114.07.19 完成施作時間：114.11.01 ---------------------------------------------------</t>
   </si>
   <si>
-    <t>2026/5/23 上午 11:41:00</t>
+    <t>2026/10/17 下午 01:48:18</t>
   </si>
   <si>
     <t>0209X-164050-A0-00-00000</t>
@@ -2479,16 +2479,16 @@
     <t>自然邊坡,RC擋土牆,其他:預力地錨</t>
   </si>
   <si>
-    <t>105年麥德姆災害 1130724凱米颱風 11407月薇帕颱風</t>
+    <t>105年麥德姆災害 1130724凱米颱風 11407月薇帕颱風 115年7月9日巴威颱風</t>
   </si>
   <si>
     <t>106/01(概估)</t>
   </si>
   <si>
-    <t>山崩與地滑地質敏感區(175K+ 400-181K+000 邊坡 ---------------------------------------------------- 災害與時間：105年麥德姆災害 災點：(177K+400) 災害編號： 施作項目：縱洩溝 開始施作時間：10506 完成施作時間：10601 ---------------------------------------------------------- 災害與時間：114.05.20豪雨災害 災點：164K+400 災害編號：113-04-A13, 114-04-B37 施作項目：縱洩溝 開始施作時間：114.07.20 完成施作時間：114.09.15</t>
-  </si>
-  <si>
-    <t>2026/5/23 上午 11:45:50</t>
+    <t>山崩與地滑地質敏感區(175K+ 400-181K+000 邊坡 ---------------------------------------------------- 災害與時間：105年麥德姆災害 災點：(177K+400) 災害編號： 施作項目：縱洩溝 開始施作時間：10506 完成施作時間：10601 ---------------------------------------------------------- 災害與時間：114.05.20豪雨災害 災點：164K+400 災害編號：113-04-A13, 114-04-B37 施作項目：縱洩溝 開始施作時間：114.07.20 完成施作時間：114.09.15 ----------------------------------------------------------------------- 災害與時間：115.07.09巴威颱風 災點：164K+400 災害編號：115-04-B53 施作項目：擋土牆及石籠網導排水搶修 開始施作時間：預定115.11.10(設計中未施作) 完成施作時間：(設計中未施作)</t>
+  </si>
+  <si>
+    <t>2026/10/17 上午 11:30:45</t>
   </si>
 </sst>
 </file>
@@ -2548,11 +2548,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="6">
-    <cellStyle name="Comma" xfId="1" xr:uid="{B0F9F5C9-F86F-334A-804C-88B68618349D}"/>
-    <cellStyle name="Comma-[0]" xfId="2" xr:uid="{2332A722-2A8C-ED45-BD50-F1E0016BBC5F}"/>
-    <cellStyle name="Currency" xfId="3" xr:uid="{467139A1-621E-004C-B01A-4C85EF60AB1C}"/>
-    <cellStyle name="Currency-[0]" xfId="4" xr:uid="{2EC9B65E-C0F1-5748-8BEB-1FB2EB5D902B}"/>
-    <cellStyle name="Percent" xfId="5" xr:uid="{72A31928-937E-CE46-ADB7-C2F17EA5DA92}"/>
+    <cellStyle name="Comma" xfId="1" xr:uid="{993CBE45-34F8-7647-A55B-393974CB0FC4}"/>
+    <cellStyle name="Comma-[0]" xfId="2" xr:uid="{7CEEB353-5C66-8149-8596-4E4F0A351FF7}"/>
+    <cellStyle name="Currency" xfId="3" xr:uid="{4FA5503D-A3B3-C94D-B14C-773CAABC9CCC}"/>
+    <cellStyle name="Currency-[0]" xfId="4" xr:uid="{F916B668-CB50-424D-B695-26201E26CC81}"/>
+    <cellStyle name="Percent" xfId="5" xr:uid="{D34B5761-41FC-914D-A05A-2D3735051EC8}"/>
     <cellStyle name="一般" xfId="0" builtinId="0" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2864,12 +2864,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C016DB7A-2690-0A41-855E-228A3D19E033}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4E82A07-1339-E64A-A23A-70D5ACB83F4C}">
   <dimension ref="A1:AH104"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="17" max="17" width="12.5" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
@@ -7679,7 +7676,7 @@
       <c r="W51" t="s">
         <v>69</v>
       </c>
-      <c r="Y51" t="s">
+      <c r="Y51" s="2" t="s">
         <v>440</v>
       </c>
       <c r="Z51" t="s">
@@ -7861,7 +7858,7 @@
         <v>80</v>
       </c>
       <c r="W53" t="s">
-        <v>69</v>
+        <v>104</v>
       </c>
       <c r="Y53" s="2" t="s">
         <v>452</v>

--- a/邊坡資料.xlsx
+++ b/邊坡資料.xlsx
@@ -1,21 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jenhanchang/SA/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\slope\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C3DF65B9-91EB-9143-B51C-6CC1B8787EF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D4278603-9A6E-43D7-AD67-4BA64DF7FA89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="820" yWindow="880" windowWidth="35180" windowHeight="22500" xr2:uid="{A041BC7A-12CC-3E4C-A1AF-B96C7640476C}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{134F0B10-E1DE-4B43-9125-2A1DFBBEDD4D}"/>
   </bookViews>
   <sheets>
     <sheet name="邊坡資料" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1018,7 +1023,7 @@
     <t>C0UA60</t>
   </si>
   <si>
-    <t>2026/1/15 下午 04:57:03</t>
+    <t>2026/10/20 下午 04:31:07</t>
   </si>
   <si>
     <t>0209DX-030150-A0-00-00000</t>
@@ -1045,7 +1050,7 @@
     <t>--------------------------------------------------------------- 災害與時間：111.10.15豪雨災害 災點：30K+200上邊坡 災害編號：111-04-B45 施作項目：刷坡100m2、掛網及錨筋灌漿100m2 開始施作時間：111.11 完成施作時間：112.01</t>
   </si>
   <si>
-    <t>2026/1/15 下午 01:53:51</t>
+    <t>2026/10/21 上午 08:19:27</t>
   </si>
   <si>
     <t>0209DX-030925-A0-00-00000</t>
@@ -1063,7 +1068,7 @@
     <t>山崩與地滑地質敏感區(133K+800~134K+400)。落石高敏感區(134K+000~134K+300)。</t>
   </si>
   <si>
-    <t>2026/1/15 下午 04:44:43</t>
+    <t>2026/10/20 下午 04:33:32</t>
   </si>
   <si>
     <t>0209DX-032180-D0-00-00000</t>
@@ -1087,7 +1092,7 @@
     <t>山崩與地滑地質敏感區(134K+900~136K+000)。落石高敏感區(134K+950~135K+ 480、135K+600~135K+750)。岩屑崩滑高敏感區(135K+520~136K+250)。 ----------------------------------------------------- 106年7月一般災害上邊坡發生坍方造成雙向道路阻斷，進行上邊坡噴凝土框植生護坡工程，於106年8月完工(135K+890~135K+920)。 ----------------------------------------------------- 107年11月2日豪雨災害造成135K+800上邊坡發生邊坡土石坍方已進行邊坡修復作業。上邊坡噴凝土框植生護坡工程於108年1月完工 災編: 107-04-B47 ----------------------------------------------------- 108年9月30日一般災害(米塔颱風災害)134K+980、135K+300、135K+580(台9丁線32.18K、32.5K、32.78K)上邊坡發生坍方，進行邊坡護坡工程(邊坡掛網及錨筋灌漿)於108年12月及1月完工。 災害編號: 108-04-B35 ----------------------------------------------------- 110年10月13日豪雨災害，32K+400處上邊坡土石崩落，施作縱洩溝，於111年3月開始施作。 災害編號：110-04-B36 --------------------------------------------------------------- 災害與時間：111.10.17豪雨災害 災點：32K+270上邊坡 災害編號：111-04-B45 施作項目：刷坡924m2、縱洩溝924m2 開始施作時間：111.11 完成施作時間：112.04 --------------------------------------------------------------- 災害與時間：111.10.17豪雨災害 災點：32K+520上邊坡 災害編號：111-04-B45 施作項目：刷坡384m2、縱洩溝 384m2 開始施作時間：111.11 完成施作時間：112.03 --------------------------------------------------------------- 災害與時間：111.10.17豪雨災害 災點：32K+380上邊坡 災害編號：111-04-B45 施作項目：刷坡200m2、掛網及錨筋灌漿200m2 開始施作時間：111.11 完成施作時間：112.01</t>
   </si>
   <si>
-    <t>2026/1/15 下午 05:04:06</t>
+    <t>2026/10/21 上午 08:24:12</t>
   </si>
   <si>
     <t>0209DX-034250-D0-00-00000</t>
@@ -1111,7 +1116,7 @@
     <t>山崩與地滑地質敏感區(137K+100-137K+300)。 --------------------------------------------------------------- 106年10月11日豪雨災害(137K+100-137+800)，進行上邊坡行框植生工程於108年7月完工。 災害編號：106-04-B25 --------------------------------------------------------------- 110年10月13日豪雨災害，34K+250處上邊坡土石崩落，施作縱洩溝，於111年3月完成施作。(災害編號：110-04-B36) --------------------------------------------------------------- 災害與時間：111.10.17豪雨災害 災點：34K+800上邊坡 災害編號：111-04-B45 施作項目：型框植生846.8m2、縱洩(橫截)溝202m2 開始施作時間：111.11 完成施作時間：112.03</t>
   </si>
   <si>
-    <t>2026/1/15 下午 05:04:19</t>
+    <t>2026/10/21 上午 08:29:11</t>
   </si>
   <si>
     <t>0209DX-035190-D0-00-00000</t>
@@ -1138,7 +1143,7 @@
     <t>岩屑崩滑高敏感區(138K+000~139K+970)。山崩與地滑地質敏感區(138K+200~138K+400、138K+600~139K+000)。 ------------------------------------------------------------- 104年9月杜鵑風災坍方阻斷已完工(139K+400)。 ------------------------------------------------------------- 110年10月13日豪雨災害造成36K+300上邊坡土石坍方，施作縱洩溝，於111年3月完成施作(災害編號：110-04-B36) -------------------------------------------------------------- 現場植生狀況良好，115年1月調降為D級。</t>
   </si>
   <si>
-    <t>2026/10/14 下午 09:21:32</t>
+    <t>2026/10/21 上午 08:57:45</t>
   </si>
   <si>
     <t>0209DX-037170-A0-00-00000</t>
@@ -2510,7 +2515,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="elffont fern"/>
+      <name val="細明體"/>
       <family val="3"/>
       <charset val="136"/>
     </font>
@@ -2548,11 +2553,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="6">
-    <cellStyle name="Comma" xfId="1" xr:uid="{993CBE45-34F8-7647-A55B-393974CB0FC4}"/>
-    <cellStyle name="Comma-[0]" xfId="2" xr:uid="{7CEEB353-5C66-8149-8596-4E4F0A351FF7}"/>
-    <cellStyle name="Currency" xfId="3" xr:uid="{4FA5503D-A3B3-C94D-B14C-773CAABC9CCC}"/>
-    <cellStyle name="Currency-[0]" xfId="4" xr:uid="{F916B668-CB50-424D-B695-26201E26CC81}"/>
-    <cellStyle name="Percent" xfId="5" xr:uid="{D34B5761-41FC-914D-A05A-2D3735051EC8}"/>
+    <cellStyle name="Comma" xfId="1" xr:uid="{BECB2BB9-C25F-44D7-AB05-C58E67B7666B}"/>
+    <cellStyle name="Comma-[0]" xfId="2" xr:uid="{5B3E84FA-B478-4AC2-A737-BE2995C17633}"/>
+    <cellStyle name="Currency" xfId="3" xr:uid="{411D5AA8-6C60-4E33-971F-ED3111359D58}"/>
+    <cellStyle name="Currency-[0]" xfId="4" xr:uid="{12CC7D24-AD54-4B41-9246-6D0E067A5187}"/>
+    <cellStyle name="Percent" xfId="5" xr:uid="{DE0BCFE4-A31D-4A38-8008-BDBE5D0279AB}"/>
     <cellStyle name="一般" xfId="0" builtinId="0" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2579,39 +2584,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -2663,7 +2668,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -2774,13 +2779,6 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -2789,6 +2787,13 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -2853,22 +2858,42 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4E82A07-1339-E64A-A23A-70D5ACB83F4C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81AA05B0-9674-49A0-8368-024B62B33E2A}">
   <dimension ref="A1:AH104"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2972,7 +2997,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>34</v>
       </c>
@@ -3061,7 +3086,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>34</v>
       </c>
@@ -3150,7 +3175,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="4" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>34</v>
       </c>
@@ -3242,7 +3267,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="5" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>34</v>
       </c>
@@ -3334,7 +3359,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="6" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>34</v>
       </c>
@@ -3429,7 +3454,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="7" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>34</v>
       </c>
@@ -3524,7 +3549,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="8" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>34</v>
       </c>
@@ -3619,7 +3644,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="9" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>34</v>
       </c>
@@ -3711,7 +3736,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="10" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>34</v>
       </c>
@@ -3803,7 +3828,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="11" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>34</v>
       </c>
@@ -3901,7 +3926,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="12" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>34</v>
       </c>
@@ -3999,7 +4024,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="13" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>34</v>
       </c>
@@ -4094,7 +4119,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="14" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>34</v>
       </c>
@@ -4189,7 +4214,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="15" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>34</v>
       </c>
@@ -4284,7 +4309,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="16" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>34</v>
       </c>
@@ -4382,7 +4407,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="17" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>34</v>
       </c>
@@ -4480,7 +4505,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="18" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>34</v>
       </c>
@@ -4578,7 +4603,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="19" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>34</v>
       </c>
@@ -4673,7 +4698,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="20" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>34</v>
       </c>
@@ -4768,7 +4793,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="21" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>34</v>
       </c>
@@ -4866,7 +4891,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="22" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>34</v>
       </c>
@@ -4958,7 +4983,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="23" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>34</v>
       </c>
@@ -5050,7 +5075,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="24" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>34</v>
       </c>
@@ -5145,7 +5170,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="25" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>34</v>
       </c>
@@ -5240,7 +5265,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="26" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>34</v>
       </c>
@@ -5338,7 +5363,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="27" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>34</v>
       </c>
@@ -5436,7 +5461,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="28" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>34</v>
       </c>
@@ -5531,7 +5556,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="29" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>34</v>
       </c>
@@ -5626,7 +5651,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="30" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>34</v>
       </c>
@@ -5721,7 +5746,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="31" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>34</v>
       </c>
@@ -5816,7 +5841,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="32" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>34</v>
       </c>
@@ -5905,7 +5930,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="33" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>34</v>
       </c>
@@ -6000,7 +6025,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="34" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>34</v>
       </c>
@@ -6095,7 +6120,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="35" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>34</v>
       </c>
@@ -6190,7 +6215,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="36" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>34</v>
       </c>
@@ -6285,7 +6310,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="37" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>34</v>
       </c>
@@ -6377,7 +6402,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="38" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>34</v>
       </c>
@@ -6472,7 +6497,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="39" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>34</v>
       </c>
@@ -6567,7 +6592,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="40" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>34</v>
       </c>
@@ -6662,7 +6687,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="41" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>34</v>
       </c>
@@ -6757,7 +6782,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="42" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>34</v>
       </c>
@@ -6855,7 +6880,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="43" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>34</v>
       </c>
@@ -6947,7 +6972,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="44" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>34</v>
       </c>
@@ -7045,7 +7070,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="45" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>34</v>
       </c>
@@ -7140,7 +7165,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="46" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>34</v>
       </c>
@@ -7238,7 +7263,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="47" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>34</v>
       </c>
@@ -7333,7 +7358,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="48" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>34</v>
       </c>
@@ -7428,7 +7453,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="49" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>34</v>
       </c>
@@ -7520,7 +7545,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="50" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>34</v>
       </c>
@@ -7612,7 +7637,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="51" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>34</v>
       </c>
@@ -7704,7 +7729,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="52" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>34</v>
       </c>
@@ -7796,7 +7821,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="53" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>34</v>
       </c>
@@ -7888,7 +7913,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="54" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>34</v>
       </c>
@@ -7983,7 +8008,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="55" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>34</v>
       </c>
@@ -8078,7 +8103,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="56" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>34</v>
       </c>
@@ -8170,7 +8195,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="57" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>34</v>
       </c>
@@ -8262,7 +8287,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="58" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>34</v>
       </c>
@@ -8360,7 +8385,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="59" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>34</v>
       </c>
@@ -8455,7 +8480,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="60" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>34</v>
       </c>
@@ -8550,7 +8575,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="61" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>34</v>
       </c>
@@ -8645,7 +8670,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="62" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>34</v>
       </c>
@@ -8740,7 +8765,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="63" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>34</v>
       </c>
@@ -8835,7 +8860,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="64" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>34</v>
       </c>
@@ -8927,7 +8952,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="65" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>34</v>
       </c>
@@ -9022,7 +9047,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="66" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>34</v>
       </c>
@@ -9117,7 +9142,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="67" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>34</v>
       </c>
@@ -9212,7 +9237,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="68" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>34</v>
       </c>
@@ -9307,7 +9332,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="69" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>34</v>
       </c>
@@ -9402,7 +9427,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="70" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>34</v>
       </c>
@@ -9503,7 +9528,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="71" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>34</v>
       </c>
@@ -9598,7 +9623,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="72" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>34</v>
       </c>
@@ -9690,7 +9715,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="73" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>34</v>
       </c>
@@ -9785,7 +9810,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="74" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>34</v>
       </c>
@@ -9880,7 +9905,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="75" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>34</v>
       </c>
@@ -9975,7 +10000,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="76" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>34</v>
       </c>
@@ -10070,7 +10095,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="77" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>34</v>
       </c>
@@ -10168,7 +10193,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="78" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>34</v>
       </c>
@@ -10263,7 +10288,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="79" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>34</v>
       </c>
@@ -10358,7 +10383,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="80" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>34</v>
       </c>
@@ -10450,7 +10475,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="81" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>34</v>
       </c>
@@ -10545,7 +10570,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="82" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>34</v>
       </c>
@@ -10637,7 +10662,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="83" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>34</v>
       </c>
@@ -10726,7 +10751,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="84" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>34</v>
       </c>
@@ -10824,7 +10849,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="85" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>34</v>
       </c>
@@ -10922,7 +10947,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="86" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>34</v>
       </c>
@@ -11014,7 +11039,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="87" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>34</v>
       </c>
@@ -11106,7 +11131,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="88" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>34</v>
       </c>
@@ -11204,7 +11229,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="89" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>34</v>
       </c>
@@ -11293,7 +11318,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="90" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>34</v>
       </c>
@@ -11388,7 +11413,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="91" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>34</v>
       </c>
@@ -11486,7 +11511,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="92" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>34</v>
       </c>
@@ -11581,7 +11606,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="93" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>34</v>
       </c>
@@ -11673,7 +11698,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="94" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>34</v>
       </c>
@@ -11765,7 +11790,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="95" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>34</v>
       </c>
@@ -11863,7 +11888,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="96" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>34</v>
       </c>
@@ -11964,7 +11989,7 @@
         <v>767</v>
       </c>
     </row>
-    <row r="97" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>34</v>
       </c>
@@ -12062,7 +12087,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="98" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>34</v>
       </c>
@@ -12160,7 +12185,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="99" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>34</v>
       </c>
@@ -12252,7 +12277,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="100" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>34</v>
       </c>
@@ -12350,7 +12375,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="101" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>34</v>
       </c>
@@ -12448,7 +12473,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="102" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>34</v>
       </c>
@@ -12543,7 +12568,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="103" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>34</v>
       </c>
@@ -12641,7 +12666,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="104" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>34</v>
       </c>

--- a/邊坡資料.xlsx
+++ b/邊坡資料.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\slope\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.134.12.60\蘇澳監工站-共用硬碟\00.南澳段工作資料-蘇澳監工站\@@(考評)(含定期巡檢)\02.邊坡\300.網頁\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D4278603-9A6E-43D7-AD67-4BA64DF7FA89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EE25A2E5-535E-42D6-8D87-7F1B5AC1FE24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{134F0B10-E1DE-4B43-9125-2A1DFBBEDD4D}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FEC58402-3529-4303-802B-2DB12E9A238E}"/>
   </bookViews>
   <sheets>
     <sheet name="邊坡資料" sheetId="1" r:id="rId1"/>
@@ -1143,7 +1143,7 @@
     <t>岩屑崩滑高敏感區(138K+000~139K+970)。山崩與地滑地質敏感區(138K+200~138K+400、138K+600~139K+000)。 ------------------------------------------------------------- 104年9月杜鵑風災坍方阻斷已完工(139K+400)。 ------------------------------------------------------------- 110年10月13日豪雨災害造成36K+300上邊坡土石坍方，施作縱洩溝，於111年3月完成施作(災害編號：110-04-B36) -------------------------------------------------------------- 現場植生狀況良好，115年1月調降為D級。</t>
   </si>
   <si>
-    <t>2026/10/21 上午 08:57:45</t>
+    <t>2026/10/21 上午 11:19:31</t>
   </si>
   <si>
     <t>0209DX-037170-A0-00-00000</t>
@@ -1167,7 +1167,7 @@
     <t>C1U850</t>
   </si>
   <si>
-    <t>2026/10/17 上午 08:41:33</t>
+    <t>2026/10/21 下午 01:33:18</t>
   </si>
   <si>
     <t>0209DX-037190-D0-00-00000</t>
@@ -1191,7 +1191,7 @@
     <t>山崩與地滑地質敏感區(139K+200-140K+700)。岩屑崩滑高敏感區(138K+000-139K+970)。 --------------------------------------------------------------- 105年3月自然災害(139.92)進行下邊坡保護工程。 災害編號：105-04-B23 --------------------------------------------------------------- 106年10月11日豪雨災害(139K+870-139K+960)。 災害編號：106-04-A10 --------------------------------------------------------------- 災害與時間：111.10.17豪雨災害 災點：37K+400下邊坡掏空 災害編號：111-04-B45 施作項目：擋土牆15.5m，路基及路面修復 開始施作時間：111.11 完成施作時間：111.12 備註：迄樁由37K+280展延至37K+450 ----------------------------------------------------------- 災害與時間：112.1.10豪雨災害 災點：37K+450下邊坡 災害編號：112-04-B06 施作項目：型框植生240m2、縱洩(橫截)溝240m2、紐澤西護欄補設26m 開始施作時間：112.1 完成施作時間：112.12</t>
   </si>
   <si>
-    <t>2026/1/15 下午 05:22:13</t>
+    <t>2026/10/21 上午 11:43:15</t>
   </si>
   <si>
     <t>0209DX-038100-A0-00-00000</t>
@@ -1239,7 +1239,7 @@
     <t>--------------------------------------------------------------- 災害與時間：112.12.4豪雨災害 災點：39K+100下邊坡 災害編號：113-04-B02 施作項目：刷坡1500m2、掛網及錨筋灌漿1500m2 開始施作時間：113.01 完成施作時間：113.04</t>
   </si>
   <si>
-    <t>2024/11/12 下午 02:15:31</t>
+    <t>2026/10/21 下午 01:18:18</t>
   </si>
   <si>
     <t>0209DX-039100-A0-00-00000</t>
@@ -1251,13 +1251,13 @@
     <t>自然邊坡,防石柵,噴凝土護坡,RC擋土牆,其他:型框植生、掛網、縱洩溝、明隧道</t>
   </si>
   <si>
-    <t>105年9月梅姬颱風災害 106年10月豪雨災害 107年5豪雨災害 108年8月23日豪雨災害 1100120豪雨災害 11104豪雨災害 11110豪雨災害 1120803豪雨災害 1140420大雨災害</t>
-  </si>
-  <si>
-    <t>山崩與地滑地質敏感區140K+800-145K+200)落石高敏感區(141K+000~141K+700、141K+850-142K+500)。已納入105年9月梅姬颱風災害進行型框植生及縱洩溝邊坡保護工法(142.5)，邊坡修復工程於106年4月完成。 -------------------------------------------------------------- 災害與時間：105年9月梅姬颱風 災點：(舊樁號142.5)上邊坡 施作項目：型框植生及縱洩溝 完成施作時間：106.04 -------------------------------------------------------------- 災害與時間：106.10豪雨災害 災點：(舊樁號1142K+150、142K+200、142K+600)上邊坡 災害編號：106-04-A10 施作項目：噴凝土、型框植生 完成施作時間：108.07 -------------------------------------------------------------- 災害與時間：107.05豪雨災害 災點：(舊樁號143K+000)上邊坡 災害編號：107-04-B17 施作項目：噴凝土 完成施作時間：108.03 -------------------------------------------------------------- 災害與時間：108.08.23豪雨災害 災點：39K+500上邊坡 災害編號：109-04-B15 施作項目：掛網及錨筋灌漿 完成施作時間：107.07 --------------------------------------------------------------- 災害與時間：110.01.20豪雨災害 災點：40K+100上邊坡 災害編號：110-04-B12 已修復竣事 -------------------------------------------------------------- 災害與時間：111.4.3豪雨災害 災點：39K+400、39K+800上邊坡 災害編號：1111-04-B17 施作項目：掛網及錨筋灌漿 開始施作時間：111.05 完成施作時間：111.08 --------------------------------------------------------------- 災害與時間：111.10.17豪雨災害 災點：39K+550上邊坡 災害編號：111-04-B45 施作項目：掛網及錨筋灌漿285m2 開始施作時間：111.11 完成施作時間：112.01 --------------------------------------------------------------- 災害與時間：111.10.17豪雨災害 災點：39K+800上邊坡 災害編號：111-04-B45 施作項目：土石清理 開始施作時間：111.10 完成施作時間：111.10 --------------------------------------------------------------- 災害與時間：112.8.3豪雨災害 災點：39K+800上邊坡 災害編號：112-04-B34 施作項目：縱洩溝5460m2 開始施作時間：112.10 完成施作時間：113.04 ---------------------------------------------------- 災害與時間：114.4.20 災點：40.250k 災害編號：114-04-B35 施作項目：噴凝土護坡及縱洩溝 開始施作時間：114.6.25 完成施作時間：114.8.16</t>
-  </si>
-  <si>
-    <t>2026/4/13 下午 02:15:45</t>
+    <t>105年9月梅姬颱風災害 106年10月豪雨災害 107年5豪雨災害 108年8月23日豪雨災害 1100120豪雨災害 11104豪雨災害 11110豪雨災害 1120803豪雨災害 1140420大雨災害 1141219豪雨災害</t>
+  </si>
+  <si>
+    <t>山崩與地滑地質敏感區140K+800-145K+200)落石高敏感區(141K+000~141K+700、141K+850-142K+500)。已納入105年9月梅姬颱風災害進行型框植生及縱洩溝邊坡保護工法(142.5)，邊坡修復工程於106年4月完成。 -------------------------------------------------------------- 災害與時間：105年9月梅姬颱風 災點：(舊樁號142.5)上邊坡 施作項目：型框植生及縱洩溝 完成施作時間：106.04 -------------------------------------------------------------- 災害與時間：106.10豪雨災害 災點：(舊樁號1142K+150、142K+200、142K+600)上邊坡 災害編號：106-04-A10 施作項目：噴凝土、型框植生 完成施作時間：108.07 -------------------------------------------------------------- 災害與時間：107.05豪雨災害 災點：(舊樁號143K+000)上邊坡 災害編號：107-04-B17 施作項目：噴凝土 完成施作時間：108.03 -------------------------------------------------------------- 災害與時間：108.08.23豪雨災害 災點：39K+500上邊坡 災害編號：109-04-B15 施作項目：掛網及錨筋灌漿 完成施作時間：107.07 --------------------------------------------------------------- 災害與時間：110.01.20豪雨災害 災點：40K+100上邊坡 災害編號：110-04-B12 已修復竣事 -------------------------------------------------------------- 災害與時間：111.4.3豪雨災害 災點：39K+400、39K+800上邊坡 災害編號：1111-04-B17 施作項目：掛網及錨筋灌漿 開始施作時間：111.05 完成施作時間：111.08 --------------------------------------------------------------- 災害與時間：111.10.17豪雨災害 災點：39K+550上邊坡 災害編號：111-04-B45 施作項目：掛網及錨筋灌漿285m2 開始施作時間：111.11 完成施作時間：112.01 --------------------------------------------------------------- 災害與時間：111.10.17豪雨災害 災點：39K+800上邊坡 災害編號：111-04-B45 施作項目：土石清理 開始施作時間：111.10 完成施作時間：111.10 --------------------------------------------------------------- 災害與時間：112.8.3豪雨災害 災點：39K+800上邊坡 災害編號：112-04-B34 施作項目：縱洩溝5460m2 開始施作時間：112.10 完成施作時間：113.04 ---------------------------------------------------- 災害與時間：114.4.20 災點：40.250k 災害編號：114-04-B35 施作項目：噴凝土護坡及縱洩溝 開始施作時間：114.6.25 完成施作時間：114.8.16 ---------------------------------------------------- 災害與時間：114.12.19 災點：39.8k 災害編號：115-04-B11 施作項目：型框植生護坡及新設涵管 開始施作時間：115.05.04 完成施作時間：115.06.16</t>
+  </si>
+  <si>
+    <t>2026/10/21 下午 01:43:24</t>
   </si>
   <si>
     <t>0209DX-040270-A0-00-00000</t>
@@ -1278,7 +1278,7 @@
     <t>山崩與地滑地質敏感區(140K+800-145K+200)。落石高敏感區(143K+000~143k+050)。岩體滑動高敏感區(143K+000~143k+310)。順向坡(143K+150~143k+310)。 ---------------------------------------------------------- 105年10月21日豪雨災害 進行縱洩溝邊坡修復(143.020)。 災害編號:105-04-B28 ---------------------------------------------------------- 108年1月1日豪雨災害造成143K+050上邊坡發生邊坡土石坍方已進行邊坡修復作業。 108.01.01一般災害 143K+050上邊坡噴凝土護坡工程於108年5月完工。 災害編號:108-04-B04。 ---------------------------------------------------------- 現場植生狀況良好，115年1月調降為D級。</t>
   </si>
   <si>
-    <t>2026/1/15 下午 05:24:00</t>
+    <t>2026/10/21 下午 01:57:06</t>
   </si>
   <si>
     <t>0209DX-040710-A0-00-00000</t>
@@ -1296,7 +1296,7 @@
     <t>岩屑崩滑高敏感區：台9線143k+470~144k+050。 落石高敏感區：台9線143k+550~143k+600。 邊坡無明顯不穩定徵兆。 --------------------------------------------------------------- 五年內無災害紀錄，奉本處四工養字第1110087350號 辦理調整至D級。</t>
   </si>
   <si>
-    <t>2026/1/15 下午 05:17:48</t>
+    <t>2026/10/21 下午 02:02:10</t>
   </si>
   <si>
     <t>0209DX-041300-A0-00-00000</t>
@@ -1317,7 +1317,7 @@
     <t>山崩與地滑地質敏感區(140K+800-145K+200)。 106年10月11日豪雨災害(144K+100)。 --------------------------------------------------------------- 災害與時間：112.8.3豪雨災害 災點：41K+420上邊坡 災害編號：112-04-B34 施作項目：縱洩溝3000m2 開始施作時間：112.10 完成施作時間：112.12</t>
   </si>
   <si>
-    <t>2026/1/15 下午 01:53:26</t>
+    <t>2026/10/21 下午 02:07:00</t>
   </si>
   <si>
     <t>0209DX-042100-D0-00-00000</t>
@@ -1335,7 +1335,7 @@
     <t>已納入105年10月21日豪雨災害，進行檔土牆保護作業(144K+900)。於106年11月完工。 災害編號：105-04-B28 --------------------------------------------------------------- 五年內無災害紀錄，奉本處四工養字第1110087350號 辦理調整至D級。</t>
   </si>
   <si>
-    <t>2026/1/15 下午 05:24:22</t>
+    <t>2026/10/21 下午 02:10:06</t>
   </si>
   <si>
     <t>0209DX-042200-A0-00-00000</t>
@@ -1353,7 +1353,7 @@
     <t>落石高敏感區(144K+950-145K+050)。山崩與地滑地質敏感區(140K+800-145K+200)。 ----------------------------------------------------------------- 111年4月3日豪雨災害42K+400上邊坡發生坍方，擬進行型框植生。(災害編號:111-04-B17)，於111年6月完成施工。</t>
   </si>
   <si>
-    <t>2026/10/17 上午 11:33:24</t>
+    <t>2026/10/21 下午 02:12:26</t>
   </si>
   <si>
     <t>0209DX-042500-D0-00-00000</t>
@@ -1374,7 +1374,7 @@
     <t>山崩與地滑地質敏感區(140K+800-145K+200)。 105年3月自然災害(145.3~145.35)進行下邊坡保護工作於106年4月完成。 災害編號：105-04-B23 --------------------------------------------------------------- 105年10月21日自然災害(145.3)進行下邊坡保護工作。 災害編號：105-04-B28 --------------------------------------------------------------- 五年內無災害紀錄，奉本處四工養字第1110087350號 辦理調整至D級。</t>
   </si>
   <si>
-    <t>2026/1/15 下午 05:24:44</t>
+    <t>2026/10/21 下午 02:14:15</t>
   </si>
   <si>
     <t>0209DX-042630-A0-00-00000</t>
@@ -1392,7 +1392,7 @@
     <t>山崩與地滑地質敏感區(145K+400-146K+200)。上邊坡坍方進行預防性上邊坡掛網及錨筋灌漿護坡工程 --------------------------------------------------------------- 災害與時間：105.10.21豪雨災害 災點：(舊樁號146K+220) 災害編號：105-04-A07 已修復竣事 (146K+207~146K+227)。 上邊坡護坡工程業於107年1月完工。 --------------------------------------------------------------- 108年9月30日(米塔颱風災害)146K+300(9丁43K+500)上邊坡發生坍坊，進行邊坡掛網及錨筋灌漿，於109年3月完工。(災害編號:108-04-B35)。 --------------------------------------------------------------- 災害與時間：110.01.20豪雨災害 災點：43K+400上邊坡 災害編號：110-04-B12 已修復竣事 --------------------------------------------------------------- 110年10月13日豪雨災害，42K+700處上邊坡土石崩落，施作型框植生，於111年3月完成施作。(災害編號：110-04-B36) ------------------------------------------------------------ 115年5月30日豪雨災害 台9丁線42k+800上邊坡，施作防落石網搶修，於115年8月11日完成施作。(災害編號：115-04-B27)</t>
   </si>
   <si>
-    <t>2026/10/17 下午 03:17:13</t>
+    <t>2026/10/21 下午 02:24:19</t>
   </si>
   <si>
     <t>0209DX-043450-D0-00-00000</t>
@@ -1416,7 +1416,7 @@
     <t>山崩與地滑地質敏感區(145K+400-146K+200)。 105年10月21日豪雨災害造成路基掏空，已進行搶修中(146.2)。 地錨、型框及噴凝土護坡工程，下邊坡護坡工程業於107年12月完工。</t>
   </si>
   <si>
-    <t>2026/1/15 下午 05:24:57</t>
+    <t>2026/10/21 下午 02:29:09</t>
   </si>
   <si>
     <t>0209DX-043800-A0-00-00000</t>
@@ -1440,7 +1440,7 @@
     <t>山崩與地滑地質敏感區(43K+820-44K+990)。 --------------------------------------------------------------- 107年11月2日豪雨災害造成146K+400、147K+100上邊坡發生邊坡土石坍方已進行邊坡修復作業。上邊坡掛網及錨筋灌漿護坡工程於108年2月完工。 災害編號：107-04-B47 --------------------------------------------------------------- 109年10月13日豪雨災害造成43K+900上邊坡發生邊坡土石坍方，擬施作縱洩溝護坡，已於110年5月完工。 災害編號：109-04-B22 ----------------------------------------------------------- 災害與時間：111.10.15豪雨災害 災點：43K+8500上邊坡 災害編號：111-04-B45 施作項目：刷坡1350m2、掛網及錨筋灌漿1350m2 開始施作時間：111.12 完成施作時間：112.04 --------------------------------------------------------------- 災害與時間：112.12.4豪雨災害 災點：43K+800上邊坡 災害編號：113-04-B02 施作項目：刷坡3996m2、噴凝土3996m2 開始施作時間：113.01 完成施作時間：113.05</t>
   </si>
   <si>
-    <t>2026/1/15 下午 05:25:12</t>
+    <t>2026/10/21 下午 02:32:34</t>
   </si>
   <si>
     <t>0209DX-043800-D0-00-00000</t>
@@ -2553,11 +2553,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="6">
-    <cellStyle name="Comma" xfId="1" xr:uid="{BECB2BB9-C25F-44D7-AB05-C58E67B7666B}"/>
-    <cellStyle name="Comma-[0]" xfId="2" xr:uid="{5B3E84FA-B478-4AC2-A737-BE2995C17633}"/>
-    <cellStyle name="Currency" xfId="3" xr:uid="{411D5AA8-6C60-4E33-971F-ED3111359D58}"/>
-    <cellStyle name="Currency-[0]" xfId="4" xr:uid="{12CC7D24-AD54-4B41-9246-6D0E067A5187}"/>
-    <cellStyle name="Percent" xfId="5" xr:uid="{DE0BCFE4-A31D-4A38-8008-BDBE5D0279AB}"/>
+    <cellStyle name="Comma" xfId="1" xr:uid="{B68851EB-11DF-42C0-B378-2F0D33E611F1}"/>
+    <cellStyle name="Comma-[0]" xfId="2" xr:uid="{0C4490F9-74CB-4D1F-BED3-8827D4E68CDC}"/>
+    <cellStyle name="Currency" xfId="3" xr:uid="{79905DDD-D939-43B5-921D-4EB0250E7719}"/>
+    <cellStyle name="Currency-[0]" xfId="4" xr:uid="{1CF95C78-6752-4F6E-962E-62B1D4586929}"/>
+    <cellStyle name="Percent" xfId="5" xr:uid="{165FD254-B3B4-4E2E-B23A-2DDECB494616}"/>
     <cellStyle name="一般" xfId="0" builtinId="0" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2889,7 +2889,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81AA05B0-9674-49A0-8368-024B62B33E2A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD2047C9-AFB2-46F5-A011-02BD23A5DF40}">
   <dimension ref="A1:AH104"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <sheetData>

--- a/邊坡資料.xlsx
+++ b/邊坡資料.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.134.12.60\蘇澳監工站-共用硬碟\00.南澳段工作資料-蘇澳監工站\@@(考評)(含定期巡檢)\02.邊坡\300.網頁\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EE25A2E5-535E-42D6-8D87-7F1B5AC1FE24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{13091E4D-AD9C-4EE9-ABA2-C2FE14992E33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FEC58402-3529-4303-802B-2DB12E9A238E}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BF26AE91-94AB-42B6-90F9-8C6BF71CA48F}"/>
   </bookViews>
   <sheets>
     <sheet name="邊坡資料" sheetId="1" r:id="rId1"/>
@@ -1431,16 +1431,16 @@
     <t>自然邊坡,防石柵,噴凝土護坡,RC擋土牆,其他:掛網、型框植生、縱洩溝、攔砂壩、砌石擋土牆</t>
   </si>
   <si>
-    <t>107年11月2日豪雨災害 109年10月13日豪雨災害 1111015豪雨災害 1121204豪雨災害</t>
+    <t>107年11月2日豪雨災害 109年10月13日豪雨災害 1111015豪雨災害 1121204豪雨災害 1141219豪雨災害</t>
   </si>
   <si>
     <t>108/02(概估)</t>
   </si>
   <si>
-    <t>山崩與地滑地質敏感區(43K+820-44K+990)。 --------------------------------------------------------------- 107年11月2日豪雨災害造成146K+400、147K+100上邊坡發生邊坡土石坍方已進行邊坡修復作業。上邊坡掛網及錨筋灌漿護坡工程於108年2月完工。 災害編號：107-04-B47 --------------------------------------------------------------- 109年10月13日豪雨災害造成43K+900上邊坡發生邊坡土石坍方，擬施作縱洩溝護坡，已於110年5月完工。 災害編號：109-04-B22 ----------------------------------------------------------- 災害與時間：111.10.15豪雨災害 災點：43K+8500上邊坡 災害編號：111-04-B45 施作項目：刷坡1350m2、掛網及錨筋灌漿1350m2 開始施作時間：111.12 完成施作時間：112.04 --------------------------------------------------------------- 災害與時間：112.12.4豪雨災害 災點：43K+800上邊坡 災害編號：113-04-B02 施作項目：刷坡3996m2、噴凝土3996m2 開始施作時間：113.01 完成施作時間：113.05</t>
-  </si>
-  <si>
-    <t>2026/10/21 下午 02:32:34</t>
+    <t>山崩與地滑地質敏感區(43K+820-44K+990)。 --------------------------------------------------------------- 107年11月2日豪雨災害造成146K+400、147K+100上邊坡發生邊坡土石坍方已進行邊坡修復作業。上邊坡掛網及錨筋灌漿護坡工程於108年2月完工。 災害編號：107-04-B47 --------------------------------------------------------------- 109年10月13日豪雨災害造成43K+900上邊坡發生邊坡土石坍方，擬施作縱洩溝護坡，已於110年5月完工。 災害編號：109-04-B22 ----------------------------------------------------------- 災害與時間：111.10.15豪雨災害 災點：43K+8500上邊坡 災害編號：111-04-B45 施作項目：刷坡1350m2、掛網及錨筋灌漿1350m2 開始施作時間：111.12 完成施作時間：112.04 --------------------------------------------------------------- 災害與時間：112.12.4豪雨災害 災點：43K+800上邊坡 災害編號：113-04-B02 施作項目：刷坡3996m2、噴凝土3996m2 開始施作時間：113.01 完成施作時間：113.05 --------------------------------------------------------------- 災害與時間：114.12.19豪雨災害 災點：44K+100上邊坡 災害編號：115-04-B11 施作項目：噴凝土護坡204m2 開始施作時間：115.03.09 完成施作時間：113.06.16</t>
+  </si>
+  <si>
+    <t>2026/10/21 下午 02:47:09</t>
   </si>
   <si>
     <t>0209DX-043800-D0-00-00000</t>
@@ -2553,11 +2553,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="6">
-    <cellStyle name="Comma" xfId="1" xr:uid="{B68851EB-11DF-42C0-B378-2F0D33E611F1}"/>
-    <cellStyle name="Comma-[0]" xfId="2" xr:uid="{0C4490F9-74CB-4D1F-BED3-8827D4E68CDC}"/>
-    <cellStyle name="Currency" xfId="3" xr:uid="{79905DDD-D939-43B5-921D-4EB0250E7719}"/>
-    <cellStyle name="Currency-[0]" xfId="4" xr:uid="{1CF95C78-6752-4F6E-962E-62B1D4586929}"/>
-    <cellStyle name="Percent" xfId="5" xr:uid="{165FD254-B3B4-4E2E-B23A-2DDECB494616}"/>
+    <cellStyle name="Comma" xfId="1" xr:uid="{4E0DE910-9669-4973-9C13-36DA66568A66}"/>
+    <cellStyle name="Comma-[0]" xfId="2" xr:uid="{CD370449-E164-4C1A-9B42-F4B065BF98CA}"/>
+    <cellStyle name="Currency" xfId="3" xr:uid="{7CDFB015-E0EE-4B86-B83A-AFEB27D46C5A}"/>
+    <cellStyle name="Currency-[0]" xfId="4" xr:uid="{2678930F-BFF5-47CF-A029-AA30CAAD1A76}"/>
+    <cellStyle name="Percent" xfId="5" xr:uid="{25F23CF8-2DD8-40C6-97EB-0343D18514C5}"/>
     <cellStyle name="一般" xfId="0" builtinId="0" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2889,7 +2889,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD2047C9-AFB2-46F5-A011-02BD23A5DF40}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{032BDD54-C668-4AA6-BE98-C83DF01DC8C9}">
   <dimension ref="A1:AH104"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -8073,7 +8073,7 @@
         <v>25</v>
       </c>
       <c r="W55" t="s">
-        <v>69</v>
+        <v>104</v>
       </c>
       <c r="Y55" s="2" t="s">
         <v>468</v>

--- a/邊坡資料.xlsx
+++ b/邊坡資料.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.134.12.60\蘇澳監工站-共用硬碟\00.南澳段工作資料-蘇澳監工站\@@(考評)(含定期巡檢)\02.邊坡\300.網頁\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{13091E4D-AD9C-4EE9-ABA2-C2FE14992E33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BBB71BDE-E3C4-42CD-BBDE-561E48B65521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BF26AE91-94AB-42B6-90F9-8C6BF71CA48F}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="22575" windowHeight="14190" xr2:uid="{A184BDC7-C6C1-44C3-928A-9C67237E6BE9}"/>
   </bookViews>
   <sheets>
     <sheet name="邊坡資料" sheetId="1" r:id="rId1"/>
@@ -1440,7 +1440,7 @@
     <t>山崩與地滑地質敏感區(43K+820-44K+990)。 --------------------------------------------------------------- 107年11月2日豪雨災害造成146K+400、147K+100上邊坡發生邊坡土石坍方已進行邊坡修復作業。上邊坡掛網及錨筋灌漿護坡工程於108年2月完工。 災害編號：107-04-B47 --------------------------------------------------------------- 109年10月13日豪雨災害造成43K+900上邊坡發生邊坡土石坍方，擬施作縱洩溝護坡，已於110年5月完工。 災害編號：109-04-B22 ----------------------------------------------------------- 災害與時間：111.10.15豪雨災害 災點：43K+8500上邊坡 災害編號：111-04-B45 施作項目：刷坡1350m2、掛網及錨筋灌漿1350m2 開始施作時間：111.12 完成施作時間：112.04 --------------------------------------------------------------- 災害與時間：112.12.4豪雨災害 災點：43K+800上邊坡 災害編號：113-04-B02 施作項目：刷坡3996m2、噴凝土3996m2 開始施作時間：113.01 完成施作時間：113.05 --------------------------------------------------------------- 災害與時間：114.12.19豪雨災害 災點：44K+100上邊坡 災害編號：115-04-B11 施作項目：噴凝土護坡204m2 開始施作時間：115.03.09 完成施作時間：113.06.16</t>
   </si>
   <si>
-    <t>2026/10/21 下午 02:47:09</t>
+    <t>2026/10/21 下午 02:57:38</t>
   </si>
   <si>
     <t>0209DX-043800-D0-00-00000</t>
@@ -1458,7 +1458,7 @@
     <t>邊坡有疑似不穩定徵兆 110年1月20日豪雨災害，43.9K處下邊坡滑動，擬設置縱洩溝、錨定混凝土框噴植基材，已於110年4月完工。(災害編號：110-04-B12 )</t>
   </si>
   <si>
-    <t>2026/1/15 下午 05:25:30</t>
+    <t>2026/10/21 下午 02:58:29</t>
   </si>
   <si>
     <t>0209DX-044300-D0-00-00000</t>
@@ -1479,13 +1479,13 @@
     <t>山崩與地滑地質敏感區(146K+400-148K+800)。 --------------------------------------------------------------- 105年10月21日豪雨災害造成下邊坡掏空。 災害與時間：105.10.21豪雨災害 災點：(舊樁號147K+100~300) 災害編號：105-04-A07 已修復竣事 --------------------------------------------------------------- 106年9月豪雨災害造成下邊坡路基坍滑，進行下邊坡擋土設施鋼軌樁防護工程(147K+100~147K+600)。 災害與時間：106.9.2豪雨災害 災點：(舊樁號147K+600) 災害編號：106-04-A09 已修復竣事 --------------------------------------------------------------- 109.4.23豪雨災害 110年6月開始專案施作基樁擋土牆與縱洩溝護坡。於111年2月竣工 災害編號：109-04-A04 ----------------------------------------------------------------</t>
   </si>
   <si>
-    <t>2026/1/15 下午 02:22:27</t>
+    <t>2026/10/21 下午 03:01:29</t>
   </si>
   <si>
     <t>0209DX-044990-A0-00-00000</t>
   </si>
   <si>
-    <t>45k+250</t>
+    <t>45k+200</t>
   </si>
   <si>
     <t>自然邊坡,RC擋土牆,其他:掛網、縱洩溝、型框植生</t>
@@ -1497,28 +1497,25 @@
     <t>105/10</t>
   </si>
   <si>
-    <t>山崩與地滑地質敏感區(146K+400-148K+800)。 -------------------------------------------------------------- 已納入105年10月21日豪雨災害(147K+800)，106年11月邊坡掛網復健完成。 災害編號：105-04-B28 -------------------------------------------------------------- 110年6月豪雨災害造成45.1K處土石滑落，施做掛網及縱洩溝，110年9月完成施作(災編110-04-B22)，於110年9月施工竣事。 -------------------------------------------------------------- 110年10月13日豪雨災害，45K+160處上邊坡土石崩落，施作型框植生，於111年3月完成施作。(災害編號：110-04-B36) -------------------------------------------------------------- 114年4月20日大雨災害，45K+050處上邊坡土石崩落，施作型框植生，於114年9月完成施作。(災害編號：114-04-B35) -------------------------------------------------------------- 114年12月19日豪雨災害，44K+100處上邊坡土石泥瀑，施作坡頂噴溝改水道保護，於115年6月底完成施作。(災害編號：115-04-B11) -------------------------------------------------------------- 114年12月19日豪雨災害，45K+150處上邊坡土石泥流，施作型框植生護坡，於115年6月底完成施作。(災害編號：115-04-B11) -------------------------------------------------------------- 114年12月19日豪雨災害，45K+250處上邊坡土石泥流，施作機械刷坡及型框植生護坡，於115年6月底完成施作。(災害編號：115-04-A04)</t>
-  </si>
-  <si>
-    <t>2026/4/13 下午 02:29:23</t>
+    <t>山崩與地滑地質敏感區(146K+400-148K+800)。 -------------------------------------------------------------- 已納入105年10月21日豪雨災害(147K+800)，106年11月邊坡掛網復健完成。 災害編號：105-04-B28 -------------------------------------------------------------- 110年6月豪雨災害造成45.1K處土石滑落，施做掛網及縱洩溝，110年9月完成施作(災編110-04-B22)，於110年9月施工竣事。 -------------------------------------------------------------- 110年10月13日豪雨災害，45K+160處上邊坡土石崩落，施作型框植生，於111年3月完成施作。(災害編號：110-04-B36) -------------------------------------------------------------- 114年4月20日大雨災害，45K+050處上邊坡土石崩落，施作型框植生，於114年9月完成施作。(災害編號：114-04-B35) -------------------------------------------------------------- 114年12月19日豪雨災害，44K+100處上邊坡土石泥瀑，施作坡頂噴溝改水道保護，於115年6月底完成施作。(災害編號：115-04-B11) -------------------------------------------------------------- 114年12月19日豪雨災害，45K+150處上邊坡土石泥流，施作型框植生護坡，於115年6月底完成施作。(災害編號：115-04-B11)</t>
+  </si>
+  <si>
+    <t>2026/10/21 下午 03:26:23</t>
   </si>
   <si>
     <t>0209DX-045200-A0-00-00000</t>
   </si>
   <si>
-    <t>45k+200</t>
-  </si>
-  <si>
     <t>45k+650</t>
   </si>
   <si>
     <t>自然邊坡,防石柵,RC擋土牆,其他:明隧道、掛網</t>
   </si>
   <si>
-    <t>山崩與地滑地質敏感區(146K+400-148K+800)。 --------------------------------------------------------------- 五年內無災害紀錄，奉本處四工養字第1110087350號 辦理調整至D級。</t>
-  </si>
-  <si>
-    <t>2026/1/15 下午 05:26:27</t>
+    <t>山崩與地滑地質敏感區(146K+400-148K+800)。 --------------------------------------------------------------- 114年12月19日豪雨災害， 45K+250處上邊坡土石泥流， 施作機械刷坡及型框植生護坡，預定115年11月底完成。 (災害編號：115-04-A04)</t>
+  </si>
+  <si>
+    <t>2026/10/21 下午 03:37:19</t>
   </si>
   <si>
     <t>0209DX-045650-A0-00-00000</t>
@@ -1539,7 +1536,7 @@
     <t>------------------------------------------------------------- 107年11月2-4日豪雨災害造成148K+300上邊坡坍方，進行邊坡掛網，於108年3月完工。(災害編號:107-04-B47)。 ------------------------------------------------------------- 108年8月26日豪雨災害造成148K+400上邊坡發生邊坡土石坍方，進行邊坡掛網工程，於109年2月完工(災害編號:108-04-B26)。 ------------------------------------------------------------- 109年12月01日豪雨災害45K+900上邊坡岩體破裂崩落，施做邊坡掛網500m2，於110年3月完工。(災害編號:110-04-B02) ------------------------------------------------------------- 現場植生狀況良好，115年1月調降為D級。</t>
   </si>
   <si>
-    <t>2026/1/15 下午 05:26:41</t>
+    <t>2026/10/21 下午 03:48:18</t>
   </si>
   <si>
     <t>0209DX-046190-A0-00-00000</t>
@@ -1566,7 +1563,7 @@
     <t>山崩與地滑地質敏感區(149K+000-152K+800)。 106年9月豪雨災害上邊坡坍方，進行上邊坡縱洩溝護坡工程(149K+350)。 災害編號：106-04-B18</t>
   </si>
   <si>
-    <t>2026/1/15 下午 05:27:03</t>
+    <t>2026/10/21 下午 03:51:30</t>
   </si>
   <si>
     <t>0209DX-046780-A0-00-00000</t>
@@ -1584,127 +1581,130 @@
     <t>山崩與地滑地質敏感區(149K+000-152K+800)。 149K+700因豪雨致土石坍方，已納入災害搶修工程進行上邊坡護坡。106年10月11日豪雨災害(149K+700)於106年9月完工，施作明隧道。 上邊坡土石鬆動易有落石影響公路行車安全，進行明隧道工程台9丁線46K+880(原149K+700)，於109年6月30日完工。</t>
   </si>
   <si>
+    <t>2026/10/21 下午 03:56:47</t>
+  </si>
+  <si>
+    <t>0209DX-046830-D0-00-00000</t>
+  </si>
+  <si>
+    <t>46k+830</t>
+  </si>
+  <si>
+    <t>46k+930</t>
+  </si>
+  <si>
+    <t>自然邊坡,RC擋土牆,其他:邊坡掛網</t>
+  </si>
+  <si>
+    <t>105年7月尼伯特風災</t>
+  </si>
+  <si>
+    <t>108/10</t>
+  </si>
+  <si>
+    <t>山崩與地滑地質敏感區(149K+000-152K+800)。已納入105年7月尼伯特風災(149.7下邊坡)進行邊坡保護工程。106年10月完工。(149K+700)。 108年於149.7下邊坡再進行邊坡保護工程於108年10月完工。 ----------------------------------------------------------------------- 現場植生狀況良好，115年1月調降為D級。</t>
+  </si>
+  <si>
+    <t>2026/1/15 下午 05:27:38</t>
+  </si>
+  <si>
+    <t>0209DX-046980-A0-00-00000</t>
+  </si>
+  <si>
+    <t>47k+795</t>
+  </si>
+  <si>
+    <t>自然邊坡,石籠護坡,RC擋土牆,其他:邊坡掛網、縱洩溝</t>
+  </si>
+  <si>
+    <t>105年9月梅姬颱風災害 106年10月11豪雨災害 11010豪雨災害 11110豪雨災害 1121204豪雨災害</t>
+  </si>
+  <si>
+    <t>110.11.10因邊坡範圍重複，將原台9丁線47K+795~47K+765併入此邊坡。 --------------------------------------------------------- 災害與時間：105.9梅姬風災 災點：(150K、150K+200)上邊坡 災害編號：106-04-A10 施作項目：縱洩溝 完成施作時間：106.08 --------------------------------------------------------- 災害與時間：106.10.11豪雨災害 災點：(149K+800)上邊坡 災害編號：106-04-A10 施作項目：邊坡掛網 完成施作時間：108.10 --------------------------------------------------------- 災害與時間：110.10.13豪雨災害 災點：47K+200上邊坡 災害編號：110-04-B36 施作項目：縱洩溝360m 開始施作時間：110.12 完成施作時間：111.03 --------------------------------------------------------- 災害與時間：111.10.15豪雨災害 災點：47K+200上邊坡 災害編號：111-04-B45 施作項目：刷坡600m2、邊坡掛網及錨筋灌漿600m2 開始施作時間：111.12 完成施作時間：112.01 --------------------------------------------------------- 災害與時間：111.10.15豪雨災害 災點：47K+100上邊坡 災害編號：111-04-B45 施作項目：刷坡1500m2、邊坡掛網及錨筋灌漿1500m2 開始施作時間：112.01 完成施作時間：112.08 --------------------------------------------------------------- 災害與時間：112.12.4豪雨災害 災點：47K+050上邊坡 災害編號：113-04-B02 施作項目：刷坡280m2、掛網及錨筋灌漿280m2 開始施作時間：113.01 完成施作時間：113.03</t>
+  </si>
+  <si>
+    <t>2026/1/15 下午 02:07:08</t>
+  </si>
+  <si>
+    <t>0209DX-047795-A0-00-00000</t>
+  </si>
+  <si>
+    <t>48k+840</t>
+  </si>
+  <si>
+    <t>自然邊坡,防石柵,RC擋土牆,其他:縱洩溝</t>
+  </si>
+  <si>
+    <t>10509梅姬風災 1130403地震災害</t>
+  </si>
+  <si>
+    <t>106/08</t>
+  </si>
+  <si>
+    <t>山崩與地滑地質敏感區(149K+000-152K+800)。 ---------------------------------------------------- 110.11.10修正里程為台9丁線47K+795~48K+840。 ---------------------------------------------------- 災害與時間：105年9月梅姬颱風 災點：(150.85、150.95) 施作項目：縱洩溝護坡 完成施作時間：106年8月 ---------------------------------------------------- 災害與時間：113.04.03地震災害 災點：48K+815上邊坡 災害編號：113-04-B13 施作項目：防落石柵修復30m 開始施作時間：113.04 完成施作時間：113.08.01</t>
+  </si>
+  <si>
+    <t>2026/10/16 上午 11:53:52</t>
+  </si>
+  <si>
+    <t>0209DX-048840-A0-00-00000</t>
+  </si>
+  <si>
+    <t>49k+040</t>
+  </si>
+  <si>
+    <t>自然邊坡,防石柵,RC擋土牆,其他:塊石疊石防護工程</t>
+  </si>
+  <si>
+    <t>108/05/29(概估)</t>
+  </si>
+  <si>
+    <t>山崩與地滑地質敏感區(149K+000-152K+800)。本案因上邊坡已逾公路範圍外，無法修復。106年9月豪雨災害邊坡坍方，進行上邊坡塊石疊石防護工程，上邊坡護坡工程業於107年8月完工，(151K+700~151K+900)。</t>
+  </si>
+  <si>
+    <t>2026/1/15 下午 05:27:50</t>
+  </si>
+  <si>
+    <t>0209DX-049040-A0-00-00000</t>
+  </si>
+  <si>
+    <t>50k+140</t>
+  </si>
+  <si>
+    <t>自然邊坡,防石柵,RC擋土牆,其他:掛網、噴凝土</t>
+  </si>
+  <si>
+    <t>1130724凱米颱風 --------------------- 因114年4月20日豪雨災害豪雨災害，南澳監工站轄線台9線49K+040~49K+950 (50K+000上邊坡)土石崩落</t>
+  </si>
+  <si>
+    <t>谷風</t>
+  </si>
+  <si>
+    <t>山崩與地滑地質敏感區(149K+000-152K+800)。 --------------------------------------------------------------- 五年內無災害紀錄，奉本處四工養字第1110087350號 辦理調整至D級。 ---------------------------------------------------- 災害與時間：113.07.24凱米颱風 災點：49K+900上邊坡 災害編號：114.6.25 施作項目：擋土牆 開始施作時間：113.12 完成施作時間：114.7.23 ---------------------------------------------------- 災害與時間：114.4.20 災點：50k+000 災害編號：114-04-B35 施作項目：土堤施作 開始施作時間：114.6.25 完成施作時間：114.10.1</t>
+  </si>
+  <si>
+    <t>2026/10/12 下午 02:05:07</t>
+  </si>
+  <si>
+    <t>0209DX-050140-A0-00-00000</t>
+  </si>
+  <si>
+    <t>50k+850</t>
+  </si>
+  <si>
+    <t>自然邊坡,RC擋土牆,其他:框型植生、掛網</t>
+  </si>
+  <si>
+    <t>10503自然災害 11010豪雨災害</t>
+  </si>
+  <si>
+    <t>澳花</t>
+  </si>
+  <si>
+    <t>山崩與地滑地質敏感區(153K+000-153K+800)。已納入105年3月自然災害災後復建(153.42k)掛網作業於106年4月完成邊坡修復工程。 110年10月13日豪雨災害，50K+810處上邊坡土石崩落，施作型框植生，於111年3月開始施作。(災害編號：110-04-B36) ---------------------------------------------------------------</t>
+  </si>
+  <si>
     <t>2026/1/15 下午 05:27:24</t>
-  </si>
-  <si>
-    <t>0209DX-046830-D0-00-00000</t>
-  </si>
-  <si>
-    <t>46k+830</t>
-  </si>
-  <si>
-    <t>46k+930</t>
-  </si>
-  <si>
-    <t>自然邊坡,RC擋土牆,其他:邊坡掛網</t>
-  </si>
-  <si>
-    <t>105年7月尼伯特風災</t>
-  </si>
-  <si>
-    <t>108/10</t>
-  </si>
-  <si>
-    <t>山崩與地滑地質敏感區(149K+000-152K+800)。已納入105年7月尼伯特風災(149.7下邊坡)進行邊坡保護工程。106年10月完工。(149K+700)。 108年於149.7下邊坡再進行邊坡保護工程於108年10月完工。 ----------------------------------------------------------------------- 現場植生狀況良好，115年1月調降為D級。</t>
-  </si>
-  <si>
-    <t>2026/1/15 下午 05:27:38</t>
-  </si>
-  <si>
-    <t>0209DX-046980-A0-00-00000</t>
-  </si>
-  <si>
-    <t>47k+795</t>
-  </si>
-  <si>
-    <t>自然邊坡,石籠護坡,RC擋土牆,其他:邊坡掛網、縱洩溝</t>
-  </si>
-  <si>
-    <t>105年9月梅姬颱風災害 106年10月11豪雨災害 11010豪雨災害 11110豪雨災害 1121204豪雨災害</t>
-  </si>
-  <si>
-    <t>110.11.10因邊坡範圍重複，將原台9丁線47K+795~47K+765併入此邊坡。 --------------------------------------------------------- 災害與時間：105.9梅姬風災 災點：(150K、150K+200)上邊坡 災害編號：106-04-A10 施作項目：縱洩溝 完成施作時間：106.08 --------------------------------------------------------- 災害與時間：106.10.11豪雨災害 災點：(149K+800)上邊坡 災害編號：106-04-A10 施作項目：邊坡掛網 完成施作時間：108.10 --------------------------------------------------------- 災害與時間：110.10.13豪雨災害 災點：47K+200上邊坡 災害編號：110-04-B36 施作項目：縱洩溝360m 開始施作時間：110.12 完成施作時間：111.03 --------------------------------------------------------- 災害與時間：111.10.15豪雨災害 災點：47K+200上邊坡 災害編號：111-04-B45 施作項目：刷坡600m2、邊坡掛網及錨筋灌漿600m2 開始施作時間：111.12 完成施作時間：112.01 --------------------------------------------------------- 災害與時間：111.10.15豪雨災害 災點：47K+100上邊坡 災害編號：111-04-B45 施作項目：刷坡1500m2、邊坡掛網及錨筋灌漿1500m2 開始施作時間：112.01 完成施作時間：112.08 --------------------------------------------------------------- 災害與時間：112.12.4豪雨災害 災點：47K+050上邊坡 災害編號：113-04-B02 施作項目：刷坡280m2、掛網及錨筋灌漿280m2 開始施作時間：113.01 完成施作時間：113.03</t>
-  </si>
-  <si>
-    <t>2026/1/15 下午 02:07:08</t>
-  </si>
-  <si>
-    <t>0209DX-047795-A0-00-00000</t>
-  </si>
-  <si>
-    <t>48k+840</t>
-  </si>
-  <si>
-    <t>自然邊坡,防石柵,RC擋土牆,其他:縱洩溝</t>
-  </si>
-  <si>
-    <t>10509梅姬風災 1130403地震災害</t>
-  </si>
-  <si>
-    <t>106/08</t>
-  </si>
-  <si>
-    <t>山崩與地滑地質敏感區(149K+000-152K+800)。 ---------------------------------------------------- 110.11.10修正里程為台9丁線47K+795~48K+840。 ---------------------------------------------------- 災害與時間：105年9月梅姬颱風 災點：(150.85、150.95) 施作項目：縱洩溝護坡 完成施作時間：106年8月 ---------------------------------------------------- 災害與時間：113.04.03地震災害 災點：48K+815上邊坡 災害編號：113-04-B13 施作項目：防落石柵修復30m 開始施作時間：113.04 完成施作時間：113.08.01</t>
-  </si>
-  <si>
-    <t>2026/10/16 上午 11:53:52</t>
-  </si>
-  <si>
-    <t>0209DX-048840-A0-00-00000</t>
-  </si>
-  <si>
-    <t>49k+040</t>
-  </si>
-  <si>
-    <t>自然邊坡,防石柵,RC擋土牆,其他:塊石疊石防護工程</t>
-  </si>
-  <si>
-    <t>108/05/29(概估)</t>
-  </si>
-  <si>
-    <t>山崩與地滑地質敏感區(149K+000-152K+800)。本案因上邊坡已逾公路範圍外，無法修復。106年9月豪雨災害邊坡坍方，進行上邊坡塊石疊石防護工程，上邊坡護坡工程業於107年8月完工，(151K+700~151K+900)。</t>
-  </si>
-  <si>
-    <t>2026/1/15 下午 05:27:50</t>
-  </si>
-  <si>
-    <t>0209DX-049040-A0-00-00000</t>
-  </si>
-  <si>
-    <t>50k+140</t>
-  </si>
-  <si>
-    <t>自然邊坡,防石柵,RC擋土牆,其他:掛網、噴凝土</t>
-  </si>
-  <si>
-    <t>1130724凱米颱風 --------------------- 因114年4月20日豪雨災害豪雨災害，南澳監工站轄線台9線49K+040~49K+950 (50K+000上邊坡)土石崩落</t>
-  </si>
-  <si>
-    <t>谷風</t>
-  </si>
-  <si>
-    <t>山崩與地滑地質敏感區(149K+000-152K+800)。 --------------------------------------------------------------- 五年內無災害紀錄，奉本處四工養字第1110087350號 辦理調整至D級。 ---------------------------------------------------- 災害與時間：113.07.24凱米颱風 災點：49K+900上邊坡 災害編號：114.6.25 施作項目：擋土牆 開始施作時間：113.12 完成施作時間：114.7.23 ---------------------------------------------------- 災害與時間：114.4.20 災點：50k+000 災害編號：114-04-B35 施作項目：土堤施作 開始施作時間：114.6.25 完成施作時間：114.10.1</t>
-  </si>
-  <si>
-    <t>2026/10/12 下午 02:05:07</t>
-  </si>
-  <si>
-    <t>0209DX-050140-A0-00-00000</t>
-  </si>
-  <si>
-    <t>50k+850</t>
-  </si>
-  <si>
-    <t>自然邊坡,RC擋土牆,其他:框型植生、掛網</t>
-  </si>
-  <si>
-    <t>10503自然災害 11010豪雨災害</t>
-  </si>
-  <si>
-    <t>澳花</t>
-  </si>
-  <si>
-    <t>山崩與地滑地質敏感區(153K+000-153K+800)。已納入105年3月自然災害災後復建(153.42k)掛網作業於106年4月完成邊坡修復工程。 110年10月13日豪雨災害，50K+810處上邊坡土石崩落，施作型框植生，於111年3月開始施作。(災害編號：110-04-B36) ---------------------------------------------------------------</t>
   </si>
   <si>
     <t>0209DX-051150-A0-00-00000</t>
@@ -2553,11 +2553,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="6">
-    <cellStyle name="Comma" xfId="1" xr:uid="{4E0DE910-9669-4973-9C13-36DA66568A66}"/>
-    <cellStyle name="Comma-[0]" xfId="2" xr:uid="{CD370449-E164-4C1A-9B42-F4B065BF98CA}"/>
-    <cellStyle name="Currency" xfId="3" xr:uid="{7CDFB015-E0EE-4B86-B83A-AFEB27D46C5A}"/>
-    <cellStyle name="Currency-[0]" xfId="4" xr:uid="{2678930F-BFF5-47CF-A029-AA30CAAD1A76}"/>
-    <cellStyle name="Percent" xfId="5" xr:uid="{25F23CF8-2DD8-40C6-97EB-0343D18514C5}"/>
+    <cellStyle name="Comma" xfId="1" xr:uid="{E846F0AA-5509-4EEF-9777-11F283E75233}"/>
+    <cellStyle name="Comma-[0]" xfId="2" xr:uid="{2F7260FC-65AE-450A-8864-9E82D5543298}"/>
+    <cellStyle name="Currency" xfId="3" xr:uid="{B4D6354D-F928-41A5-AF8E-E568821A5FBA}"/>
+    <cellStyle name="Currency-[0]" xfId="4" xr:uid="{6C6BEE53-52A5-476E-969B-1909D8138B4D}"/>
+    <cellStyle name="Percent" xfId="5" xr:uid="{79C63EE2-F9EB-4260-90A2-E7478DFABDFC}"/>
     <cellStyle name="一般" xfId="0" builtinId="0" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2889,7 +2889,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{032BDD54-C668-4AA6-BE98-C83DF01DC8C9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F65DBAE3-31C8-484D-97CE-477F13A8ED28}">
   <dimension ref="A1:AH104"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -8408,10 +8408,10 @@
         <v>88</v>
       </c>
       <c r="H59" t="s">
+        <v>486</v>
+      </c>
+      <c r="I59" t="s">
         <v>493</v>
-      </c>
-      <c r="I59" t="s">
-        <v>494</v>
       </c>
       <c r="J59" t="s">
         <v>43</v>
@@ -8432,7 +8432,7 @@
         <v>24.359961200000001</v>
       </c>
       <c r="P59" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="Q59" t="s">
         <v>92</v>
@@ -8450,7 +8450,7 @@
         <v>80</v>
       </c>
       <c r="W59" t="s">
-        <v>48</v>
+        <v>104</v>
       </c>
       <c r="Y59" t="s">
         <v>49</v>
@@ -8471,13 +8471,13 @@
         <v>461</v>
       </c>
       <c r="AF59" s="2" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="AG59" t="s">
         <v>379</v>
       </c>
       <c r="AH59" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="60" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8485,7 +8485,7 @@
         <v>34</v>
       </c>
       <c r="B60" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C60" t="s">
         <v>36</v>
@@ -8503,10 +8503,10 @@
         <v>88</v>
       </c>
       <c r="H60" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="I60" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="J60" t="s">
         <v>43</v>
@@ -8527,7 +8527,7 @@
         <v>24.356542000000001</v>
       </c>
       <c r="P60" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="Q60" t="s">
         <v>92</v>
@@ -8548,10 +8548,10 @@
         <v>48</v>
       </c>
       <c r="Y60" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="Z60" t="s">
         <v>501</v>
-      </c>
-      <c r="Z60" t="s">
-        <v>502</v>
       </c>
       <c r="AA60" t="s">
         <v>72</v>
@@ -8566,13 +8566,13 @@
         <v>461</v>
       </c>
       <c r="AF60" s="2" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="AG60" t="s">
         <v>379</v>
       </c>
       <c r="AH60" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="61" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8580,7 +8580,7 @@
         <v>34</v>
       </c>
       <c r="B61" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C61" t="s">
         <v>36</v>
@@ -8598,10 +8598,10 @@
         <v>88</v>
       </c>
       <c r="H61" t="s">
+        <v>505</v>
+      </c>
+      <c r="I61" t="s">
         <v>506</v>
-      </c>
-      <c r="I61" t="s">
-        <v>507</v>
       </c>
       <c r="J61" t="s">
         <v>43</v>
@@ -8622,7 +8622,7 @@
         <v>24.350852700000001</v>
       </c>
       <c r="P61" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="Q61" t="s">
         <v>92</v>
@@ -8643,10 +8643,10 @@
         <v>48</v>
       </c>
       <c r="Y61" t="s">
+        <v>508</v>
+      </c>
+      <c r="Z61" t="s">
         <v>509</v>
-      </c>
-      <c r="Z61" t="s">
-        <v>510</v>
       </c>
       <c r="AA61" t="s">
         <v>72</v>
@@ -8658,16 +8658,16 @@
         <v>49</v>
       </c>
       <c r="AE61" t="s">
+        <v>510</v>
+      </c>
+      <c r="AF61" s="2" t="s">
         <v>511</v>
-      </c>
-      <c r="AF61" s="2" t="s">
-        <v>512</v>
       </c>
       <c r="AG61" t="s">
         <v>379</v>
       </c>
       <c r="AH61" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="62" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8675,7 +8675,7 @@
         <v>34</v>
       </c>
       <c r="B62" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C62" t="s">
         <v>36</v>
@@ -8693,10 +8693,10 @@
         <v>88</v>
       </c>
       <c r="H62" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="I62" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="J62" t="s">
         <v>43</v>
@@ -8717,7 +8717,7 @@
         <v>24.349626399999998</v>
       </c>
       <c r="P62" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="Q62" t="s">
         <v>92</v>
@@ -8738,7 +8738,7 @@
         <v>48</v>
       </c>
       <c r="Y62" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="Z62" t="s">
         <v>153</v>
@@ -8753,16 +8753,16 @@
         <v>49</v>
       </c>
       <c r="AE62" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="AF62" s="2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="AG62" t="s">
         <v>379</v>
       </c>
       <c r="AH62" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="63" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8770,7 +8770,7 @@
         <v>34</v>
       </c>
       <c r="B63" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C63" t="s">
         <v>36</v>
@@ -8788,10 +8788,10 @@
         <v>88</v>
       </c>
       <c r="H63" t="s">
+        <v>520</v>
+      </c>
+      <c r="I63" t="s">
         <v>521</v>
-      </c>
-      <c r="I63" t="s">
-        <v>522</v>
       </c>
       <c r="J63" t="s">
         <v>57</v>
@@ -8812,7 +8812,7 @@
         <v>24.350055999999999</v>
       </c>
       <c r="P63" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="Q63" t="s">
         <v>92</v>
@@ -8833,10 +8833,10 @@
         <v>48</v>
       </c>
       <c r="Y63" t="s">
+        <v>523</v>
+      </c>
+      <c r="Z63" t="s">
         <v>524</v>
-      </c>
-      <c r="Z63" t="s">
-        <v>525</v>
       </c>
       <c r="AA63" t="s">
         <v>72</v>
@@ -8848,16 +8848,16 @@
         <v>49</v>
       </c>
       <c r="AE63" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="AF63" s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="AG63" t="s">
         <v>379</v>
       </c>
       <c r="AH63" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="64" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8865,7 +8865,7 @@
         <v>34</v>
       </c>
       <c r="B64" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C64" t="s">
         <v>36</v>
@@ -8883,10 +8883,10 @@
         <v>88</v>
       </c>
       <c r="H64" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="I64" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="J64" t="s">
         <v>43</v>
@@ -8907,7 +8907,7 @@
         <v>24.3449396</v>
       </c>
       <c r="P64" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="Q64" t="s">
         <v>92</v>
@@ -8925,10 +8925,10 @@
         <v>69</v>
       </c>
       <c r="Y64" s="2" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="Z64" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AA64" t="s">
         <v>213</v>
@@ -8940,16 +8940,16 @@
         <v>49</v>
       </c>
       <c r="AE64" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="AF64" s="2" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="AG64" t="s">
         <v>379</v>
       </c>
       <c r="AH64" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="65" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8957,7 +8957,7 @@
         <v>34</v>
       </c>
       <c r="B65" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C65" t="s">
         <v>36</v>
@@ -8975,10 +8975,10 @@
         <v>88</v>
       </c>
       <c r="H65" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="I65" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="J65" t="s">
         <v>43</v>
@@ -8999,7 +8999,7 @@
         <v>24.336224300000001</v>
       </c>
       <c r="P65" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="Q65" t="s">
         <v>92</v>
@@ -9020,10 +9020,10 @@
         <v>69</v>
       </c>
       <c r="Y65" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="Z65" t="s">
         <v>537</v>
-      </c>
-      <c r="Z65" t="s">
-        <v>538</v>
       </c>
       <c r="AA65" t="s">
         <v>213</v>
@@ -9035,16 +9035,16 @@
         <v>49</v>
       </c>
       <c r="AE65" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="AF65" s="2" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="AG65" t="s">
         <v>379</v>
       </c>
       <c r="AH65" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="66" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9052,7 +9052,7 @@
         <v>34</v>
       </c>
       <c r="B66" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C66" t="s">
         <v>36</v>
@@ -9070,10 +9070,10 @@
         <v>88</v>
       </c>
       <c r="H66" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="I66" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="J66" t="s">
         <v>43</v>
@@ -9094,7 +9094,7 @@
         <v>24.334509300000001</v>
       </c>
       <c r="P66" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="Q66" t="s">
         <v>92</v>
@@ -9115,10 +9115,10 @@
         <v>48</v>
       </c>
       <c r="Y66" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="Z66" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="AA66" t="s">
         <v>72</v>
@@ -9130,16 +9130,16 @@
         <v>49</v>
       </c>
       <c r="AE66" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="AF66" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="AG66" t="s">
         <v>379</v>
       </c>
       <c r="AH66" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="67" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9147,7 +9147,7 @@
         <v>34</v>
       </c>
       <c r="B67" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C67" t="s">
         <v>36</v>
@@ -9165,10 +9165,10 @@
         <v>88</v>
       </c>
       <c r="H67" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="I67" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="J67" t="s">
         <v>43</v>
@@ -9189,7 +9189,7 @@
         <v>24.3266928</v>
       </c>
       <c r="P67" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="Q67" t="s">
         <v>92</v>
@@ -9210,7 +9210,7 @@
         <v>104</v>
       </c>
       <c r="Y67" s="2" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="Z67" t="s">
         <v>386</v>
@@ -9225,16 +9225,16 @@
         <v>49</v>
       </c>
       <c r="AE67" t="s">
+        <v>550</v>
+      </c>
+      <c r="AF67" s="2" t="s">
         <v>551</v>
-      </c>
-      <c r="AF67" s="2" t="s">
-        <v>552</v>
       </c>
       <c r="AG67" t="s">
         <v>379</v>
       </c>
       <c r="AH67" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="68" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9242,7 +9242,7 @@
         <v>34</v>
       </c>
       <c r="B68" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C68" t="s">
         <v>36</v>
@@ -9260,10 +9260,10 @@
         <v>88</v>
       </c>
       <c r="H68" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="I68" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="J68" t="s">
         <v>43</v>
@@ -9284,7 +9284,7 @@
         <v>24.321846900000001</v>
       </c>
       <c r="P68" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="Q68" t="s">
         <v>92</v>
@@ -9305,7 +9305,7 @@
         <v>69</v>
       </c>
       <c r="Y68" s="2" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="Z68" t="s">
         <v>115</v>
@@ -9320,16 +9320,16 @@
         <v>49</v>
       </c>
       <c r="AE68" t="s">
+        <v>557</v>
+      </c>
+      <c r="AF68" s="2" t="s">
         <v>558</v>
-      </c>
-      <c r="AF68" s="2" t="s">
-        <v>559</v>
       </c>
       <c r="AG68" t="s">
         <v>379</v>
       </c>
       <c r="AH68" t="s">
-        <v>519</v>
+        <v>559</v>
       </c>
     </row>
     <row r="69" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9415,7 +9415,7 @@
         <v>49</v>
       </c>
       <c r="AE69" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="AF69" s="2" t="s">
         <v>566</v>
@@ -11487,7 +11487,7 @@
         <v>727</v>
       </c>
       <c r="Z91" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="AA91" t="s">
         <v>72</v>
